--- a/code/resultados/NWJSSP_OADG_NEH(InsertionUPMixedImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(InsertionUPMixedImprovement).xlsx
@@ -15,6 +15,11 @@
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tai_j1000_m10_1" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,6 +461,5000 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6383030</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3603513</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>17214</v>
+      </c>
+      <c r="B2" t="n">
+        <v>52260</v>
+      </c>
+      <c r="C2" t="n">
+        <v>68920</v>
+      </c>
+      <c r="D2" t="n">
+        <v>125695</v>
+      </c>
+      <c r="E2" t="n">
+        <v>107366</v>
+      </c>
+      <c r="F2" t="n">
+        <v>70807</v>
+      </c>
+      <c r="G2" t="n">
+        <v>99425</v>
+      </c>
+      <c r="H2" t="n">
+        <v>95424</v>
+      </c>
+      <c r="I2" t="n">
+        <v>81042</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1555</v>
+      </c>
+      <c r="K2" t="n">
+        <v>43376</v>
+      </c>
+      <c r="L2" t="n">
+        <v>69862</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12471</v>
+      </c>
+      <c r="N2" t="n">
+        <v>77048</v>
+      </c>
+      <c r="O2" t="n">
+        <v>54271</v>
+      </c>
+      <c r="P2" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>57888</v>
+      </c>
+      <c r="R2" t="n">
+        <v>37683</v>
+      </c>
+      <c r="S2" t="n">
+        <v>49550</v>
+      </c>
+      <c r="T2" t="n">
+        <v>29847</v>
+      </c>
+      <c r="U2" t="n">
+        <v>111506</v>
+      </c>
+      <c r="V2" t="n">
+        <v>37258</v>
+      </c>
+      <c r="W2" t="n">
+        <v>66240</v>
+      </c>
+      <c r="X2" t="n">
+        <v>93296</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>117691</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>21278</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>47171</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>75107</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>15765</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4676</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>41151</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>86321</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>114456</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>61518</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>33675</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>99351</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>88078</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>97228</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>20135</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>83379</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>9525</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>26558</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>128224</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>124364</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>61216</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>74198</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9857</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>28781</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>109055</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>64433</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>71967</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>80536</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>85677</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>45477</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>22140</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>11308</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6336</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>22080</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>48462</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>46666</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>32926</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2741</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>51795</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>43180</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>44972</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>57845</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>109000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>103033</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>26078</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>89501</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>93010</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6124</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>72954</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>89649</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>119844</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>55788</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>85993</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>58062</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>122383</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>30221</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>35931</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>93062</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>18406</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>80359</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>15376</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>8132</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>116838</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>37485</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>102015</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>755</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>5677</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>42017</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>66253</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>111995</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>77012</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>105408</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>62505</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>26925</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44478592</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3613559</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>304539</v>
+      </c>
+      <c r="B2" t="n">
+        <v>217347</v>
+      </c>
+      <c r="C2" t="n">
+        <v>357783</v>
+      </c>
+      <c r="D2" t="n">
+        <v>348909</v>
+      </c>
+      <c r="E2" t="n">
+        <v>480197</v>
+      </c>
+      <c r="F2" t="n">
+        <v>751850</v>
+      </c>
+      <c r="G2" t="n">
+        <v>315433</v>
+      </c>
+      <c r="H2" t="n">
+        <v>494524</v>
+      </c>
+      <c r="I2" t="n">
+        <v>680325</v>
+      </c>
+      <c r="J2" t="n">
+        <v>605382</v>
+      </c>
+      <c r="K2" t="n">
+        <v>641209</v>
+      </c>
+      <c r="L2" t="n">
+        <v>46603</v>
+      </c>
+      <c r="M2" t="n">
+        <v>775549</v>
+      </c>
+      <c r="N2" t="n">
+        <v>413876</v>
+      </c>
+      <c r="O2" t="n">
+        <v>803508</v>
+      </c>
+      <c r="P2" t="n">
+        <v>718889</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>842356</v>
+      </c>
+      <c r="R2" t="n">
+        <v>744623</v>
+      </c>
+      <c r="S2" t="n">
+        <v>166695</v>
+      </c>
+      <c r="T2" t="n">
+        <v>658</v>
+      </c>
+      <c r="U2" t="n">
+        <v>767447</v>
+      </c>
+      <c r="V2" t="n">
+        <v>484193</v>
+      </c>
+      <c r="W2" t="n">
+        <v>446212</v>
+      </c>
+      <c r="X2" t="n">
+        <v>582462</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>281059</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>441332</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>813524</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>342648</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>642827</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>552397</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>125651</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>246611</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>711092</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>377928</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>62750</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>546121</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>417938</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>399807</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>195761</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>70223</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>244063</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>186690</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>26878</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>266448</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>367664</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>130442</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>443082</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>687264</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>149423</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>518665</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>73017</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>115284</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>575331</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>381390</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>28717</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>89214</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>546268</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>124496</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>668091</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>8436</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>705176</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>211738</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>858134</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>192547</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>745043</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>90587</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>154340</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>98037</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>232833</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>620591</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>633936</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>327094</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>464350</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>535329</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>302297</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>412552</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>15282</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>829092</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>368</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>585076</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>504829</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>492551</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>608853</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>4325</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>111987</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>784375</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>54006</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>224840</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>660033</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>435001</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>735818</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>30792</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>189793</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>277509</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>477980</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>642188</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>266277</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>807838</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>307426</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44103185</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3604213</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>39700</v>
+      </c>
+      <c r="B2" t="n">
+        <v>762671</v>
+      </c>
+      <c r="C2" t="n">
+        <v>573956</v>
+      </c>
+      <c r="D2" t="n">
+        <v>194715</v>
+      </c>
+      <c r="E2" t="n">
+        <v>300794</v>
+      </c>
+      <c r="F2" t="n">
+        <v>421214</v>
+      </c>
+      <c r="G2" t="n">
+        <v>740881</v>
+      </c>
+      <c r="H2" t="n">
+        <v>580968</v>
+      </c>
+      <c r="I2" t="n">
+        <v>128773</v>
+      </c>
+      <c r="J2" t="n">
+        <v>327076</v>
+      </c>
+      <c r="K2" t="n">
+        <v>822272</v>
+      </c>
+      <c r="L2" t="n">
+        <v>374135</v>
+      </c>
+      <c r="M2" t="n">
+        <v>751371</v>
+      </c>
+      <c r="N2" t="n">
+        <v>799456</v>
+      </c>
+      <c r="O2" t="n">
+        <v>815398</v>
+      </c>
+      <c r="P2" t="n">
+        <v>332949</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>371637</v>
+      </c>
+      <c r="R2" t="n">
+        <v>89288</v>
+      </c>
+      <c r="S2" t="n">
+        <v>682032</v>
+      </c>
+      <c r="T2" t="n">
+        <v>20848</v>
+      </c>
+      <c r="U2" t="n">
+        <v>58431</v>
+      </c>
+      <c r="V2" t="n">
+        <v>518914</v>
+      </c>
+      <c r="W2" t="n">
+        <v>318030</v>
+      </c>
+      <c r="X2" t="n">
+        <v>285198</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>594935</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>72696</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>684769</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>537987</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>451273</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>771629</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>642698</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>262223</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>435211</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>716275</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>477408</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>503704</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>350394</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>433679</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>383216</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>422745</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>15419</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>402468</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>334211</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>364172</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>274974</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9253</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>776032</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>145654</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>175233</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>701405</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>525553</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>318574</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>504799</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>722441</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>216651</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2115</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>584908</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>40819</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>633049</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>267811</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>848933</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>421339</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>223219</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>118058</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>128779</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>26001</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>181972</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>550527</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>665849</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>104813</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>96610</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>473684</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>242178</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>401741</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>596173</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>48039</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>403710</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>208575</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>542933</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>159115</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>325682</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>618620</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>527728</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>229507</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>163183</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>232478</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>78754</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>84204</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>659572</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>464304</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>640028</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>285868</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>59523</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>168867</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>794727</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>473515</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>695913</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>501900</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>590806</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>590549781</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3947240</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
+      <c r="CW1" t="inlineStr"/>
+      <c r="CX1" t="inlineStr"/>
+      <c r="CY1" t="inlineStr"/>
+      <c r="CZ1" t="inlineStr"/>
+      <c r="DA1" t="inlineStr"/>
+      <c r="DB1" t="inlineStr"/>
+      <c r="DC1" t="inlineStr"/>
+      <c r="DD1" t="inlineStr"/>
+      <c r="DE1" t="inlineStr"/>
+      <c r="DF1" t="inlineStr"/>
+      <c r="DG1" t="inlineStr"/>
+      <c r="DH1" t="inlineStr"/>
+      <c r="DI1" t="inlineStr"/>
+      <c r="DJ1" t="inlineStr"/>
+      <c r="DK1" t="inlineStr"/>
+      <c r="DL1" t="inlineStr"/>
+      <c r="DM1" t="inlineStr"/>
+      <c r="DN1" t="inlineStr"/>
+      <c r="DO1" t="inlineStr"/>
+      <c r="DP1" t="inlineStr"/>
+      <c r="DQ1" t="inlineStr"/>
+      <c r="DR1" t="inlineStr"/>
+      <c r="DS1" t="inlineStr"/>
+      <c r="DT1" t="inlineStr"/>
+      <c r="DU1" t="inlineStr"/>
+      <c r="DV1" t="inlineStr"/>
+      <c r="DW1" t="inlineStr"/>
+      <c r="DX1" t="inlineStr"/>
+      <c r="DY1" t="inlineStr"/>
+      <c r="DZ1" t="inlineStr"/>
+      <c r="EA1" t="inlineStr"/>
+      <c r="EB1" t="inlineStr"/>
+      <c r="EC1" t="inlineStr"/>
+      <c r="ED1" t="inlineStr"/>
+      <c r="EE1" t="inlineStr"/>
+      <c r="EF1" t="inlineStr"/>
+      <c r="EG1" t="inlineStr"/>
+      <c r="EH1" t="inlineStr"/>
+      <c r="EI1" t="inlineStr"/>
+      <c r="EJ1" t="inlineStr"/>
+      <c r="EK1" t="inlineStr"/>
+      <c r="EL1" t="inlineStr"/>
+      <c r="EM1" t="inlineStr"/>
+      <c r="EN1" t="inlineStr"/>
+      <c r="EO1" t="inlineStr"/>
+      <c r="EP1" t="inlineStr"/>
+      <c r="EQ1" t="inlineStr"/>
+      <c r="ER1" t="inlineStr"/>
+      <c r="ES1" t="inlineStr"/>
+      <c r="ET1" t="inlineStr"/>
+      <c r="EU1" t="inlineStr"/>
+      <c r="EV1" t="inlineStr"/>
+      <c r="EW1" t="inlineStr"/>
+      <c r="EX1" t="inlineStr"/>
+      <c r="EY1" t="inlineStr"/>
+      <c r="EZ1" t="inlineStr"/>
+      <c r="FA1" t="inlineStr"/>
+      <c r="FB1" t="inlineStr"/>
+      <c r="FC1" t="inlineStr"/>
+      <c r="FD1" t="inlineStr"/>
+      <c r="FE1" t="inlineStr"/>
+      <c r="FF1" t="inlineStr"/>
+      <c r="FG1" t="inlineStr"/>
+      <c r="FH1" t="inlineStr"/>
+      <c r="FI1" t="inlineStr"/>
+      <c r="FJ1" t="inlineStr"/>
+      <c r="FK1" t="inlineStr"/>
+      <c r="FL1" t="inlineStr"/>
+      <c r="FM1" t="inlineStr"/>
+      <c r="FN1" t="inlineStr"/>
+      <c r="FO1" t="inlineStr"/>
+      <c r="FP1" t="inlineStr"/>
+      <c r="FQ1" t="inlineStr"/>
+      <c r="FR1" t="inlineStr"/>
+      <c r="FS1" t="inlineStr"/>
+      <c r="FT1" t="inlineStr"/>
+      <c r="FU1" t="inlineStr"/>
+      <c r="FV1" t="inlineStr"/>
+      <c r="FW1" t="inlineStr"/>
+      <c r="FX1" t="inlineStr"/>
+      <c r="FY1" t="inlineStr"/>
+      <c r="FZ1" t="inlineStr"/>
+      <c r="GA1" t="inlineStr"/>
+      <c r="GB1" t="inlineStr"/>
+      <c r="GC1" t="inlineStr"/>
+      <c r="GD1" t="inlineStr"/>
+      <c r="GE1" t="inlineStr"/>
+      <c r="GF1" t="inlineStr"/>
+      <c r="GG1" t="inlineStr"/>
+      <c r="GH1" t="inlineStr"/>
+      <c r="GI1" t="inlineStr"/>
+      <c r="GJ1" t="inlineStr"/>
+      <c r="GK1" t="inlineStr"/>
+      <c r="GL1" t="inlineStr"/>
+      <c r="GM1" t="inlineStr"/>
+      <c r="GN1" t="inlineStr"/>
+      <c r="GO1" t="inlineStr"/>
+      <c r="GP1" t="inlineStr"/>
+      <c r="GQ1" t="inlineStr"/>
+      <c r="GR1" t="inlineStr"/>
+      <c r="GS1" t="inlineStr"/>
+      <c r="GT1" t="inlineStr"/>
+      <c r="GU1" t="inlineStr"/>
+      <c r="GV1" t="inlineStr"/>
+      <c r="GW1" t="inlineStr"/>
+      <c r="GX1" t="inlineStr"/>
+      <c r="GY1" t="inlineStr"/>
+      <c r="GZ1" t="inlineStr"/>
+      <c r="HA1" t="inlineStr"/>
+      <c r="HB1" t="inlineStr"/>
+      <c r="HC1" t="inlineStr"/>
+      <c r="HD1" t="inlineStr"/>
+      <c r="HE1" t="inlineStr"/>
+      <c r="HF1" t="inlineStr"/>
+      <c r="HG1" t="inlineStr"/>
+      <c r="HH1" t="inlineStr"/>
+      <c r="HI1" t="inlineStr"/>
+      <c r="HJ1" t="inlineStr"/>
+      <c r="HK1" t="inlineStr"/>
+      <c r="HL1" t="inlineStr"/>
+      <c r="HM1" t="inlineStr"/>
+      <c r="HN1" t="inlineStr"/>
+      <c r="HO1" t="inlineStr"/>
+      <c r="HP1" t="inlineStr"/>
+      <c r="HQ1" t="inlineStr"/>
+      <c r="HR1" t="inlineStr"/>
+      <c r="HS1" t="inlineStr"/>
+      <c r="HT1" t="inlineStr"/>
+      <c r="HU1" t="inlineStr"/>
+      <c r="HV1" t="inlineStr"/>
+      <c r="HW1" t="inlineStr"/>
+      <c r="HX1" t="inlineStr"/>
+      <c r="HY1" t="inlineStr"/>
+      <c r="HZ1" t="inlineStr"/>
+      <c r="IA1" t="inlineStr"/>
+      <c r="IB1" t="inlineStr"/>
+      <c r="IC1" t="inlineStr"/>
+      <c r="ID1" t="inlineStr"/>
+      <c r="IE1" t="inlineStr"/>
+      <c r="IF1" t="inlineStr"/>
+      <c r="IG1" t="inlineStr"/>
+      <c r="IH1" t="inlineStr"/>
+      <c r="II1" t="inlineStr"/>
+      <c r="IJ1" t="inlineStr"/>
+      <c r="IK1" t="inlineStr"/>
+      <c r="IL1" t="inlineStr"/>
+      <c r="IM1" t="inlineStr"/>
+      <c r="IN1" t="inlineStr"/>
+      <c r="IO1" t="inlineStr"/>
+      <c r="IP1" t="inlineStr"/>
+      <c r="IQ1" t="inlineStr"/>
+      <c r="IR1" t="inlineStr"/>
+      <c r="IS1" t="inlineStr"/>
+      <c r="IT1" t="inlineStr"/>
+      <c r="IU1" t="inlineStr"/>
+      <c r="IV1" t="inlineStr"/>
+      <c r="IW1" t="inlineStr"/>
+      <c r="IX1" t="inlineStr"/>
+      <c r="IY1" t="inlineStr"/>
+      <c r="IZ1" t="inlineStr"/>
+      <c r="JA1" t="inlineStr"/>
+      <c r="JB1" t="inlineStr"/>
+      <c r="JC1" t="inlineStr"/>
+      <c r="JD1" t="inlineStr"/>
+      <c r="JE1" t="inlineStr"/>
+      <c r="JF1" t="inlineStr"/>
+      <c r="JG1" t="inlineStr"/>
+      <c r="JH1" t="inlineStr"/>
+      <c r="JI1" t="inlineStr"/>
+      <c r="JJ1" t="inlineStr"/>
+      <c r="JK1" t="inlineStr"/>
+      <c r="JL1" t="inlineStr"/>
+      <c r="JM1" t="inlineStr"/>
+      <c r="JN1" t="inlineStr"/>
+      <c r="JO1" t="inlineStr"/>
+      <c r="JP1" t="inlineStr"/>
+      <c r="JQ1" t="inlineStr"/>
+      <c r="JR1" t="inlineStr"/>
+      <c r="JS1" t="inlineStr"/>
+      <c r="JT1" t="inlineStr"/>
+      <c r="JU1" t="inlineStr"/>
+      <c r="JV1" t="inlineStr"/>
+      <c r="JW1" t="inlineStr"/>
+      <c r="JX1" t="inlineStr"/>
+      <c r="JY1" t="inlineStr"/>
+      <c r="JZ1" t="inlineStr"/>
+      <c r="KA1" t="inlineStr"/>
+      <c r="KB1" t="inlineStr"/>
+      <c r="KC1" t="inlineStr"/>
+      <c r="KD1" t="inlineStr"/>
+      <c r="KE1" t="inlineStr"/>
+      <c r="KF1" t="inlineStr"/>
+      <c r="KG1" t="inlineStr"/>
+      <c r="KH1" t="inlineStr"/>
+      <c r="KI1" t="inlineStr"/>
+      <c r="KJ1" t="inlineStr"/>
+      <c r="KK1" t="inlineStr"/>
+      <c r="KL1" t="inlineStr"/>
+      <c r="KM1" t="inlineStr"/>
+      <c r="KN1" t="inlineStr"/>
+      <c r="KO1" t="inlineStr"/>
+      <c r="KP1" t="inlineStr"/>
+      <c r="KQ1" t="inlineStr"/>
+      <c r="KR1" t="inlineStr"/>
+      <c r="KS1" t="inlineStr"/>
+      <c r="KT1" t="inlineStr"/>
+      <c r="KU1" t="inlineStr"/>
+      <c r="KV1" t="inlineStr"/>
+      <c r="KW1" t="inlineStr"/>
+      <c r="KX1" t="inlineStr"/>
+      <c r="KY1" t="inlineStr"/>
+      <c r="KZ1" t="inlineStr"/>
+      <c r="LA1" t="inlineStr"/>
+      <c r="LB1" t="inlineStr"/>
+      <c r="LC1" t="inlineStr"/>
+      <c r="LD1" t="inlineStr"/>
+      <c r="LE1" t="inlineStr"/>
+      <c r="LF1" t="inlineStr"/>
+      <c r="LG1" t="inlineStr"/>
+      <c r="LH1" t="inlineStr"/>
+      <c r="LI1" t="inlineStr"/>
+      <c r="LJ1" t="inlineStr"/>
+      <c r="LK1" t="inlineStr"/>
+      <c r="LL1" t="inlineStr"/>
+      <c r="LM1" t="inlineStr"/>
+      <c r="LN1" t="inlineStr"/>
+      <c r="LO1" t="inlineStr"/>
+      <c r="LP1" t="inlineStr"/>
+      <c r="LQ1" t="inlineStr"/>
+      <c r="LR1" t="inlineStr"/>
+      <c r="LS1" t="inlineStr"/>
+      <c r="LT1" t="inlineStr"/>
+      <c r="LU1" t="inlineStr"/>
+      <c r="LV1" t="inlineStr"/>
+      <c r="LW1" t="inlineStr"/>
+      <c r="LX1" t="inlineStr"/>
+      <c r="LY1" t="inlineStr"/>
+      <c r="LZ1" t="inlineStr"/>
+      <c r="MA1" t="inlineStr"/>
+      <c r="MB1" t="inlineStr"/>
+      <c r="MC1" t="inlineStr"/>
+      <c r="MD1" t="inlineStr"/>
+      <c r="ME1" t="inlineStr"/>
+      <c r="MF1" t="inlineStr"/>
+      <c r="MG1" t="inlineStr"/>
+      <c r="MH1" t="inlineStr"/>
+      <c r="MI1" t="inlineStr"/>
+      <c r="MJ1" t="inlineStr"/>
+      <c r="MK1" t="inlineStr"/>
+      <c r="ML1" t="inlineStr"/>
+      <c r="MM1" t="inlineStr"/>
+      <c r="MN1" t="inlineStr"/>
+      <c r="MO1" t="inlineStr"/>
+      <c r="MP1" t="inlineStr"/>
+      <c r="MQ1" t="inlineStr"/>
+      <c r="MR1" t="inlineStr"/>
+      <c r="MS1" t="inlineStr"/>
+      <c r="MT1" t="inlineStr"/>
+      <c r="MU1" t="inlineStr"/>
+      <c r="MV1" t="inlineStr"/>
+      <c r="MW1" t="inlineStr"/>
+      <c r="MX1" t="inlineStr"/>
+      <c r="MY1" t="inlineStr"/>
+      <c r="MZ1" t="inlineStr"/>
+      <c r="NA1" t="inlineStr"/>
+      <c r="NB1" t="inlineStr"/>
+      <c r="NC1" t="inlineStr"/>
+      <c r="ND1" t="inlineStr"/>
+      <c r="NE1" t="inlineStr"/>
+      <c r="NF1" t="inlineStr"/>
+      <c r="NG1" t="inlineStr"/>
+      <c r="NH1" t="inlineStr"/>
+      <c r="NI1" t="inlineStr"/>
+      <c r="NJ1" t="inlineStr"/>
+      <c r="NK1" t="inlineStr"/>
+      <c r="NL1" t="inlineStr"/>
+      <c r="NM1" t="inlineStr"/>
+      <c r="NN1" t="inlineStr"/>
+      <c r="NO1" t="inlineStr"/>
+      <c r="NP1" t="inlineStr"/>
+      <c r="NQ1" t="inlineStr"/>
+      <c r="NR1" t="inlineStr"/>
+      <c r="NS1" t="inlineStr"/>
+      <c r="NT1" t="inlineStr"/>
+      <c r="NU1" t="inlineStr"/>
+      <c r="NV1" t="inlineStr"/>
+      <c r="NW1" t="inlineStr"/>
+      <c r="NX1" t="inlineStr"/>
+      <c r="NY1" t="inlineStr"/>
+      <c r="NZ1" t="inlineStr"/>
+      <c r="OA1" t="inlineStr"/>
+      <c r="OB1" t="inlineStr"/>
+      <c r="OC1" t="inlineStr"/>
+      <c r="OD1" t="inlineStr"/>
+      <c r="OE1" t="inlineStr"/>
+      <c r="OF1" t="inlineStr"/>
+      <c r="OG1" t="inlineStr"/>
+      <c r="OH1" t="inlineStr"/>
+      <c r="OI1" t="inlineStr"/>
+      <c r="OJ1" t="inlineStr"/>
+      <c r="OK1" t="inlineStr"/>
+      <c r="OL1" t="inlineStr"/>
+      <c r="OM1" t="inlineStr"/>
+      <c r="ON1" t="inlineStr"/>
+      <c r="OO1" t="inlineStr"/>
+      <c r="OP1" t="inlineStr"/>
+      <c r="OQ1" t="inlineStr"/>
+      <c r="OR1" t="inlineStr"/>
+      <c r="OS1" t="inlineStr"/>
+      <c r="OT1" t="inlineStr"/>
+      <c r="OU1" t="inlineStr"/>
+      <c r="OV1" t="inlineStr"/>
+      <c r="OW1" t="inlineStr"/>
+      <c r="OX1" t="inlineStr"/>
+      <c r="OY1" t="inlineStr"/>
+      <c r="OZ1" t="inlineStr"/>
+      <c r="PA1" t="inlineStr"/>
+      <c r="PB1" t="inlineStr"/>
+      <c r="PC1" t="inlineStr"/>
+      <c r="PD1" t="inlineStr"/>
+      <c r="PE1" t="inlineStr"/>
+      <c r="PF1" t="inlineStr"/>
+      <c r="PG1" t="inlineStr"/>
+      <c r="PH1" t="inlineStr"/>
+      <c r="PI1" t="inlineStr"/>
+      <c r="PJ1" t="inlineStr"/>
+      <c r="PK1" t="inlineStr"/>
+      <c r="PL1" t="inlineStr"/>
+      <c r="PM1" t="inlineStr"/>
+      <c r="PN1" t="inlineStr"/>
+      <c r="PO1" t="inlineStr"/>
+      <c r="PP1" t="inlineStr"/>
+      <c r="PQ1" t="inlineStr"/>
+      <c r="PR1" t="inlineStr"/>
+      <c r="PS1" t="inlineStr"/>
+      <c r="PT1" t="inlineStr"/>
+      <c r="PU1" t="inlineStr"/>
+      <c r="PV1" t="inlineStr"/>
+      <c r="PW1" t="inlineStr"/>
+      <c r="PX1" t="inlineStr"/>
+      <c r="PY1" t="inlineStr"/>
+      <c r="PZ1" t="inlineStr"/>
+      <c r="QA1" t="inlineStr"/>
+      <c r="QB1" t="inlineStr"/>
+      <c r="QC1" t="inlineStr"/>
+      <c r="QD1" t="inlineStr"/>
+      <c r="QE1" t="inlineStr"/>
+      <c r="QF1" t="inlineStr"/>
+      <c r="QG1" t="inlineStr"/>
+      <c r="QH1" t="inlineStr"/>
+      <c r="QI1" t="inlineStr"/>
+      <c r="QJ1" t="inlineStr"/>
+      <c r="QK1" t="inlineStr"/>
+      <c r="QL1" t="inlineStr"/>
+      <c r="QM1" t="inlineStr"/>
+      <c r="QN1" t="inlineStr"/>
+      <c r="QO1" t="inlineStr"/>
+      <c r="QP1" t="inlineStr"/>
+      <c r="QQ1" t="inlineStr"/>
+      <c r="QR1" t="inlineStr"/>
+      <c r="QS1" t="inlineStr"/>
+      <c r="QT1" t="inlineStr"/>
+      <c r="QU1" t="inlineStr"/>
+      <c r="QV1" t="inlineStr"/>
+      <c r="QW1" t="inlineStr"/>
+      <c r="QX1" t="inlineStr"/>
+      <c r="QY1" t="inlineStr"/>
+      <c r="QZ1" t="inlineStr"/>
+      <c r="RA1" t="inlineStr"/>
+      <c r="RB1" t="inlineStr"/>
+      <c r="RC1" t="inlineStr"/>
+      <c r="RD1" t="inlineStr"/>
+      <c r="RE1" t="inlineStr"/>
+      <c r="RF1" t="inlineStr"/>
+      <c r="RG1" t="inlineStr"/>
+      <c r="RH1" t="inlineStr"/>
+      <c r="RI1" t="inlineStr"/>
+      <c r="RJ1" t="inlineStr"/>
+      <c r="RK1" t="inlineStr"/>
+      <c r="RL1" t="inlineStr"/>
+      <c r="RM1" t="inlineStr"/>
+      <c r="RN1" t="inlineStr"/>
+      <c r="RO1" t="inlineStr"/>
+      <c r="RP1" t="inlineStr"/>
+      <c r="RQ1" t="inlineStr"/>
+      <c r="RR1" t="inlineStr"/>
+      <c r="RS1" t="inlineStr"/>
+      <c r="RT1" t="inlineStr"/>
+      <c r="RU1" t="inlineStr"/>
+      <c r="RV1" t="inlineStr"/>
+      <c r="RW1" t="inlineStr"/>
+      <c r="RX1" t="inlineStr"/>
+      <c r="RY1" t="inlineStr"/>
+      <c r="RZ1" t="inlineStr"/>
+      <c r="SA1" t="inlineStr"/>
+      <c r="SB1" t="inlineStr"/>
+      <c r="SC1" t="inlineStr"/>
+      <c r="SD1" t="inlineStr"/>
+      <c r="SE1" t="inlineStr"/>
+      <c r="SF1" t="inlineStr"/>
+      <c r="SG1" t="inlineStr"/>
+      <c r="SH1" t="inlineStr"/>
+      <c r="SI1" t="inlineStr"/>
+      <c r="SJ1" t="inlineStr"/>
+      <c r="SK1" t="inlineStr"/>
+      <c r="SL1" t="inlineStr"/>
+      <c r="SM1" t="inlineStr"/>
+      <c r="SN1" t="inlineStr"/>
+      <c r="SO1" t="inlineStr"/>
+      <c r="SP1" t="inlineStr"/>
+      <c r="SQ1" t="inlineStr"/>
+      <c r="SR1" t="inlineStr"/>
+      <c r="SS1" t="inlineStr"/>
+      <c r="ST1" t="inlineStr"/>
+      <c r="SU1" t="inlineStr"/>
+      <c r="SV1" t="inlineStr"/>
+      <c r="SW1" t="inlineStr"/>
+      <c r="SX1" t="inlineStr"/>
+      <c r="SY1" t="inlineStr"/>
+      <c r="SZ1" t="inlineStr"/>
+      <c r="TA1" t="inlineStr"/>
+      <c r="TB1" t="inlineStr"/>
+      <c r="TC1" t="inlineStr"/>
+      <c r="TD1" t="inlineStr"/>
+      <c r="TE1" t="inlineStr"/>
+      <c r="TF1" t="inlineStr"/>
+      <c r="TG1" t="inlineStr"/>
+      <c r="TH1" t="inlineStr"/>
+      <c r="TI1" t="inlineStr"/>
+      <c r="TJ1" t="inlineStr"/>
+      <c r="TK1" t="inlineStr"/>
+      <c r="TL1" t="inlineStr"/>
+      <c r="TM1" t="inlineStr"/>
+      <c r="TN1" t="inlineStr"/>
+      <c r="TO1" t="inlineStr"/>
+      <c r="TP1" t="inlineStr"/>
+      <c r="TQ1" t="inlineStr"/>
+      <c r="TR1" t="inlineStr"/>
+      <c r="TS1" t="inlineStr"/>
+      <c r="TT1" t="inlineStr"/>
+      <c r="TU1" t="inlineStr"/>
+      <c r="TV1" t="inlineStr"/>
+      <c r="TW1" t="inlineStr"/>
+      <c r="TX1" t="inlineStr"/>
+      <c r="TY1" t="inlineStr"/>
+      <c r="TZ1" t="inlineStr"/>
+      <c r="UA1" t="inlineStr"/>
+      <c r="UB1" t="inlineStr"/>
+      <c r="UC1" t="inlineStr"/>
+      <c r="UD1" t="inlineStr"/>
+      <c r="UE1" t="inlineStr"/>
+      <c r="UF1" t="inlineStr"/>
+      <c r="UG1" t="inlineStr"/>
+      <c r="UH1" t="inlineStr"/>
+      <c r="UI1" t="inlineStr"/>
+      <c r="UJ1" t="inlineStr"/>
+      <c r="UK1" t="inlineStr"/>
+      <c r="UL1" t="inlineStr"/>
+      <c r="UM1" t="inlineStr"/>
+      <c r="UN1" t="inlineStr"/>
+      <c r="UO1" t="inlineStr"/>
+      <c r="UP1" t="inlineStr"/>
+      <c r="UQ1" t="inlineStr"/>
+      <c r="UR1" t="inlineStr"/>
+      <c r="US1" t="inlineStr"/>
+      <c r="UT1" t="inlineStr"/>
+      <c r="UU1" t="inlineStr"/>
+      <c r="UV1" t="inlineStr"/>
+      <c r="UW1" t="inlineStr"/>
+      <c r="UX1" t="inlineStr"/>
+      <c r="UY1" t="inlineStr"/>
+      <c r="UZ1" t="inlineStr"/>
+      <c r="VA1" t="inlineStr"/>
+      <c r="VB1" t="inlineStr"/>
+      <c r="VC1" t="inlineStr"/>
+      <c r="VD1" t="inlineStr"/>
+      <c r="VE1" t="inlineStr"/>
+      <c r="VF1" t="inlineStr"/>
+      <c r="VG1" t="inlineStr"/>
+      <c r="VH1" t="inlineStr"/>
+      <c r="VI1" t="inlineStr"/>
+      <c r="VJ1" t="inlineStr"/>
+      <c r="VK1" t="inlineStr"/>
+      <c r="VL1" t="inlineStr"/>
+      <c r="VM1" t="inlineStr"/>
+      <c r="VN1" t="inlineStr"/>
+      <c r="VO1" t="inlineStr"/>
+      <c r="VP1" t="inlineStr"/>
+      <c r="VQ1" t="inlineStr"/>
+      <c r="VR1" t="inlineStr"/>
+      <c r="VS1" t="inlineStr"/>
+      <c r="VT1" t="inlineStr"/>
+      <c r="VU1" t="inlineStr"/>
+      <c r="VV1" t="inlineStr"/>
+      <c r="VW1" t="inlineStr"/>
+      <c r="VX1" t="inlineStr"/>
+      <c r="VY1" t="inlineStr"/>
+      <c r="VZ1" t="inlineStr"/>
+      <c r="WA1" t="inlineStr"/>
+      <c r="WB1" t="inlineStr"/>
+      <c r="WC1" t="inlineStr"/>
+      <c r="WD1" t="inlineStr"/>
+      <c r="WE1" t="inlineStr"/>
+      <c r="WF1" t="inlineStr"/>
+      <c r="WG1" t="inlineStr"/>
+      <c r="WH1" t="inlineStr"/>
+      <c r="WI1" t="inlineStr"/>
+      <c r="WJ1" t="inlineStr"/>
+      <c r="WK1" t="inlineStr"/>
+      <c r="WL1" t="inlineStr"/>
+      <c r="WM1" t="inlineStr"/>
+      <c r="WN1" t="inlineStr"/>
+      <c r="WO1" t="inlineStr"/>
+      <c r="WP1" t="inlineStr"/>
+      <c r="WQ1" t="inlineStr"/>
+      <c r="WR1" t="inlineStr"/>
+      <c r="WS1" t="inlineStr"/>
+      <c r="WT1" t="inlineStr"/>
+      <c r="WU1" t="inlineStr"/>
+      <c r="WV1" t="inlineStr"/>
+      <c r="WW1" t="inlineStr"/>
+      <c r="WX1" t="inlineStr"/>
+      <c r="WY1" t="inlineStr"/>
+      <c r="WZ1" t="inlineStr"/>
+      <c r="XA1" t="inlineStr"/>
+      <c r="XB1" t="inlineStr"/>
+      <c r="XC1" t="inlineStr"/>
+      <c r="XD1" t="inlineStr"/>
+      <c r="XE1" t="inlineStr"/>
+      <c r="XF1" t="inlineStr"/>
+      <c r="XG1" t="inlineStr"/>
+      <c r="XH1" t="inlineStr"/>
+      <c r="XI1" t="inlineStr"/>
+      <c r="XJ1" t="inlineStr"/>
+      <c r="XK1" t="inlineStr"/>
+      <c r="XL1" t="inlineStr"/>
+      <c r="XM1" t="inlineStr"/>
+      <c r="XN1" t="inlineStr"/>
+      <c r="XO1" t="inlineStr"/>
+      <c r="XP1" t="inlineStr"/>
+      <c r="XQ1" t="inlineStr"/>
+      <c r="XR1" t="inlineStr"/>
+      <c r="XS1" t="inlineStr"/>
+      <c r="XT1" t="inlineStr"/>
+      <c r="XU1" t="inlineStr"/>
+      <c r="XV1" t="inlineStr"/>
+      <c r="XW1" t="inlineStr"/>
+      <c r="XX1" t="inlineStr"/>
+      <c r="XY1" t="inlineStr"/>
+      <c r="XZ1" t="inlineStr"/>
+      <c r="YA1" t="inlineStr"/>
+      <c r="YB1" t="inlineStr"/>
+      <c r="YC1" t="inlineStr"/>
+      <c r="YD1" t="inlineStr"/>
+      <c r="YE1" t="inlineStr"/>
+      <c r="YF1" t="inlineStr"/>
+      <c r="YG1" t="inlineStr"/>
+      <c r="YH1" t="inlineStr"/>
+      <c r="YI1" t="inlineStr"/>
+      <c r="YJ1" t="inlineStr"/>
+      <c r="YK1" t="inlineStr"/>
+      <c r="YL1" t="inlineStr"/>
+      <c r="YM1" t="inlineStr"/>
+      <c r="YN1" t="inlineStr"/>
+      <c r="YO1" t="inlineStr"/>
+      <c r="YP1" t="inlineStr"/>
+      <c r="YQ1" t="inlineStr"/>
+      <c r="YR1" t="inlineStr"/>
+      <c r="YS1" t="inlineStr"/>
+      <c r="YT1" t="inlineStr"/>
+      <c r="YU1" t="inlineStr"/>
+      <c r="YV1" t="inlineStr"/>
+      <c r="YW1" t="inlineStr"/>
+      <c r="YX1" t="inlineStr"/>
+      <c r="YY1" t="inlineStr"/>
+      <c r="YZ1" t="inlineStr"/>
+      <c r="ZA1" t="inlineStr"/>
+      <c r="ZB1" t="inlineStr"/>
+      <c r="ZC1" t="inlineStr"/>
+      <c r="ZD1" t="inlineStr"/>
+      <c r="ZE1" t="inlineStr"/>
+      <c r="ZF1" t="inlineStr"/>
+      <c r="ZG1" t="inlineStr"/>
+      <c r="ZH1" t="inlineStr"/>
+      <c r="ZI1" t="inlineStr"/>
+      <c r="ZJ1" t="inlineStr"/>
+      <c r="ZK1" t="inlineStr"/>
+      <c r="ZL1" t="inlineStr"/>
+      <c r="ZM1" t="inlineStr"/>
+      <c r="ZN1" t="inlineStr"/>
+      <c r="ZO1" t="inlineStr"/>
+      <c r="ZP1" t="inlineStr"/>
+      <c r="ZQ1" t="inlineStr"/>
+      <c r="ZR1" t="inlineStr"/>
+      <c r="ZS1" t="inlineStr"/>
+      <c r="ZT1" t="inlineStr"/>
+      <c r="ZU1" t="inlineStr"/>
+      <c r="ZV1" t="inlineStr"/>
+      <c r="ZW1" t="inlineStr"/>
+      <c r="ZX1" t="inlineStr"/>
+      <c r="ZY1" t="inlineStr"/>
+      <c r="ZZ1" t="inlineStr"/>
+      <c r="AAA1" t="inlineStr"/>
+      <c r="AAB1" t="inlineStr"/>
+      <c r="AAC1" t="inlineStr"/>
+      <c r="AAD1" t="inlineStr"/>
+      <c r="AAE1" t="inlineStr"/>
+      <c r="AAF1" t="inlineStr"/>
+      <c r="AAG1" t="inlineStr"/>
+      <c r="AAH1" t="inlineStr"/>
+      <c r="AAI1" t="inlineStr"/>
+      <c r="AAJ1" t="inlineStr"/>
+      <c r="AAK1" t="inlineStr"/>
+      <c r="AAL1" t="inlineStr"/>
+      <c r="AAM1" t="inlineStr"/>
+      <c r="AAN1" t="inlineStr"/>
+      <c r="AAO1" t="inlineStr"/>
+      <c r="AAP1" t="inlineStr"/>
+      <c r="AAQ1" t="inlineStr"/>
+      <c r="AAR1" t="inlineStr"/>
+      <c r="AAS1" t="inlineStr"/>
+      <c r="AAT1" t="inlineStr"/>
+      <c r="AAU1" t="inlineStr"/>
+      <c r="AAV1" t="inlineStr"/>
+      <c r="AAW1" t="inlineStr"/>
+      <c r="AAX1" t="inlineStr"/>
+      <c r="AAY1" t="inlineStr"/>
+      <c r="AAZ1" t="inlineStr"/>
+      <c r="ABA1" t="inlineStr"/>
+      <c r="ABB1" t="inlineStr"/>
+      <c r="ABC1" t="inlineStr"/>
+      <c r="ABD1" t="inlineStr"/>
+      <c r="ABE1" t="inlineStr"/>
+      <c r="ABF1" t="inlineStr"/>
+      <c r="ABG1" t="inlineStr"/>
+      <c r="ABH1" t="inlineStr"/>
+      <c r="ABI1" t="inlineStr"/>
+      <c r="ABJ1" t="inlineStr"/>
+      <c r="ABK1" t="inlineStr"/>
+      <c r="ABL1" t="inlineStr"/>
+      <c r="ABM1" t="inlineStr"/>
+      <c r="ABN1" t="inlineStr"/>
+      <c r="ABO1" t="inlineStr"/>
+      <c r="ABP1" t="inlineStr"/>
+      <c r="ABQ1" t="inlineStr"/>
+      <c r="ABR1" t="inlineStr"/>
+      <c r="ABS1" t="inlineStr"/>
+      <c r="ABT1" t="inlineStr"/>
+      <c r="ABU1" t="inlineStr"/>
+      <c r="ABV1" t="inlineStr"/>
+      <c r="ABW1" t="inlineStr"/>
+      <c r="ABX1" t="inlineStr"/>
+      <c r="ABY1" t="inlineStr"/>
+      <c r="ABZ1" t="inlineStr"/>
+      <c r="ACA1" t="inlineStr"/>
+      <c r="ACB1" t="inlineStr"/>
+      <c r="ACC1" t="inlineStr"/>
+      <c r="ACD1" t="inlineStr"/>
+      <c r="ACE1" t="inlineStr"/>
+      <c r="ACF1" t="inlineStr"/>
+      <c r="ACG1" t="inlineStr"/>
+      <c r="ACH1" t="inlineStr"/>
+      <c r="ACI1" t="inlineStr"/>
+      <c r="ACJ1" t="inlineStr"/>
+      <c r="ACK1" t="inlineStr"/>
+      <c r="ACL1" t="inlineStr"/>
+      <c r="ACM1" t="inlineStr"/>
+      <c r="ACN1" t="inlineStr"/>
+      <c r="ACO1" t="inlineStr"/>
+      <c r="ACP1" t="inlineStr"/>
+      <c r="ACQ1" t="inlineStr"/>
+      <c r="ACR1" t="inlineStr"/>
+      <c r="ACS1" t="inlineStr"/>
+      <c r="ACT1" t="inlineStr"/>
+      <c r="ACU1" t="inlineStr"/>
+      <c r="ACV1" t="inlineStr"/>
+      <c r="ACW1" t="inlineStr"/>
+      <c r="ACX1" t="inlineStr"/>
+      <c r="ACY1" t="inlineStr"/>
+      <c r="ACZ1" t="inlineStr"/>
+      <c r="ADA1" t="inlineStr"/>
+      <c r="ADB1" t="inlineStr"/>
+      <c r="ADC1" t="inlineStr"/>
+      <c r="ADD1" t="inlineStr"/>
+      <c r="ADE1" t="inlineStr"/>
+      <c r="ADF1" t="inlineStr"/>
+      <c r="ADG1" t="inlineStr"/>
+      <c r="ADH1" t="inlineStr"/>
+      <c r="ADI1" t="inlineStr"/>
+      <c r="ADJ1" t="inlineStr"/>
+      <c r="ADK1" t="inlineStr"/>
+      <c r="ADL1" t="inlineStr"/>
+      <c r="ADM1" t="inlineStr"/>
+      <c r="ADN1" t="inlineStr"/>
+      <c r="ADO1" t="inlineStr"/>
+      <c r="ADP1" t="inlineStr"/>
+      <c r="ADQ1" t="inlineStr"/>
+      <c r="ADR1" t="inlineStr"/>
+      <c r="ADS1" t="inlineStr"/>
+      <c r="ADT1" t="inlineStr"/>
+      <c r="ADU1" t="inlineStr"/>
+      <c r="ADV1" t="inlineStr"/>
+      <c r="ADW1" t="inlineStr"/>
+      <c r="ADX1" t="inlineStr"/>
+      <c r="ADY1" t="inlineStr"/>
+      <c r="ADZ1" t="inlineStr"/>
+      <c r="AEA1" t="inlineStr"/>
+      <c r="AEB1" t="inlineStr"/>
+      <c r="AEC1" t="inlineStr"/>
+      <c r="AED1" t="inlineStr"/>
+      <c r="AEE1" t="inlineStr"/>
+      <c r="AEF1" t="inlineStr"/>
+      <c r="AEG1" t="inlineStr"/>
+      <c r="AEH1" t="inlineStr"/>
+      <c r="AEI1" t="inlineStr"/>
+      <c r="AEJ1" t="inlineStr"/>
+      <c r="AEK1" t="inlineStr"/>
+      <c r="AEL1" t="inlineStr"/>
+      <c r="AEM1" t="inlineStr"/>
+      <c r="AEN1" t="inlineStr"/>
+      <c r="AEO1" t="inlineStr"/>
+      <c r="AEP1" t="inlineStr"/>
+      <c r="AEQ1" t="inlineStr"/>
+      <c r="AER1" t="inlineStr"/>
+      <c r="AES1" t="inlineStr"/>
+      <c r="AET1" t="inlineStr"/>
+      <c r="AEU1" t="inlineStr"/>
+      <c r="AEV1" t="inlineStr"/>
+      <c r="AEW1" t="inlineStr"/>
+      <c r="AEX1" t="inlineStr"/>
+      <c r="AEY1" t="inlineStr"/>
+      <c r="AEZ1" t="inlineStr"/>
+      <c r="AFA1" t="inlineStr"/>
+      <c r="AFB1" t="inlineStr"/>
+      <c r="AFC1" t="inlineStr"/>
+      <c r="AFD1" t="inlineStr"/>
+      <c r="AFE1" t="inlineStr"/>
+      <c r="AFF1" t="inlineStr"/>
+      <c r="AFG1" t="inlineStr"/>
+      <c r="AFH1" t="inlineStr"/>
+      <c r="AFI1" t="inlineStr"/>
+      <c r="AFJ1" t="inlineStr"/>
+      <c r="AFK1" t="inlineStr"/>
+      <c r="AFL1" t="inlineStr"/>
+      <c r="AFM1" t="inlineStr"/>
+      <c r="AFN1" t="inlineStr"/>
+      <c r="AFO1" t="inlineStr"/>
+      <c r="AFP1" t="inlineStr"/>
+      <c r="AFQ1" t="inlineStr"/>
+      <c r="AFR1" t="inlineStr"/>
+      <c r="AFS1" t="inlineStr"/>
+      <c r="AFT1" t="inlineStr"/>
+      <c r="AFU1" t="inlineStr"/>
+      <c r="AFV1" t="inlineStr"/>
+      <c r="AFW1" t="inlineStr"/>
+      <c r="AFX1" t="inlineStr"/>
+      <c r="AFY1" t="inlineStr"/>
+      <c r="AFZ1" t="inlineStr"/>
+      <c r="AGA1" t="inlineStr"/>
+      <c r="AGB1" t="inlineStr"/>
+      <c r="AGC1" t="inlineStr"/>
+      <c r="AGD1" t="inlineStr"/>
+      <c r="AGE1" t="inlineStr"/>
+      <c r="AGF1" t="inlineStr"/>
+      <c r="AGG1" t="inlineStr"/>
+      <c r="AGH1" t="inlineStr"/>
+      <c r="AGI1" t="inlineStr"/>
+      <c r="AGJ1" t="inlineStr"/>
+      <c r="AGK1" t="inlineStr"/>
+      <c r="AGL1" t="inlineStr"/>
+      <c r="AGM1" t="inlineStr"/>
+      <c r="AGN1" t="inlineStr"/>
+      <c r="AGO1" t="inlineStr"/>
+      <c r="AGP1" t="inlineStr"/>
+      <c r="AGQ1" t="inlineStr"/>
+      <c r="AGR1" t="inlineStr"/>
+      <c r="AGS1" t="inlineStr"/>
+      <c r="AGT1" t="inlineStr"/>
+      <c r="AGU1" t="inlineStr"/>
+      <c r="AGV1" t="inlineStr"/>
+      <c r="AGW1" t="inlineStr"/>
+      <c r="AGX1" t="inlineStr"/>
+      <c r="AGY1" t="inlineStr"/>
+      <c r="AGZ1" t="inlineStr"/>
+      <c r="AHA1" t="inlineStr"/>
+      <c r="AHB1" t="inlineStr"/>
+      <c r="AHC1" t="inlineStr"/>
+      <c r="AHD1" t="inlineStr"/>
+      <c r="AHE1" t="inlineStr"/>
+      <c r="AHF1" t="inlineStr"/>
+      <c r="AHG1" t="inlineStr"/>
+      <c r="AHH1" t="inlineStr"/>
+      <c r="AHI1" t="inlineStr"/>
+      <c r="AHJ1" t="inlineStr"/>
+      <c r="AHK1" t="inlineStr"/>
+      <c r="AHL1" t="inlineStr"/>
+      <c r="AHM1" t="inlineStr"/>
+      <c r="AHN1" t="inlineStr"/>
+      <c r="AHO1" t="inlineStr"/>
+      <c r="AHP1" t="inlineStr"/>
+      <c r="AHQ1" t="inlineStr"/>
+      <c r="AHR1" t="inlineStr"/>
+      <c r="AHS1" t="inlineStr"/>
+      <c r="AHT1" t="inlineStr"/>
+      <c r="AHU1" t="inlineStr"/>
+      <c r="AHV1" t="inlineStr"/>
+      <c r="AHW1" t="inlineStr"/>
+      <c r="AHX1" t="inlineStr"/>
+      <c r="AHY1" t="inlineStr"/>
+      <c r="AHZ1" t="inlineStr"/>
+      <c r="AIA1" t="inlineStr"/>
+      <c r="AIB1" t="inlineStr"/>
+      <c r="AIC1" t="inlineStr"/>
+      <c r="AID1" t="inlineStr"/>
+      <c r="AIE1" t="inlineStr"/>
+      <c r="AIF1" t="inlineStr"/>
+      <c r="AIG1" t="inlineStr"/>
+      <c r="AIH1" t="inlineStr"/>
+      <c r="AII1" t="inlineStr"/>
+      <c r="AIJ1" t="inlineStr"/>
+      <c r="AIK1" t="inlineStr"/>
+      <c r="AIL1" t="inlineStr"/>
+      <c r="AIM1" t="inlineStr"/>
+      <c r="AIN1" t="inlineStr"/>
+      <c r="AIO1" t="inlineStr"/>
+      <c r="AIP1" t="inlineStr"/>
+      <c r="AIQ1" t="inlineStr"/>
+      <c r="AIR1" t="inlineStr"/>
+      <c r="AIS1" t="inlineStr"/>
+      <c r="AIT1" t="inlineStr"/>
+      <c r="AIU1" t="inlineStr"/>
+      <c r="AIV1" t="inlineStr"/>
+      <c r="AIW1" t="inlineStr"/>
+      <c r="AIX1" t="inlineStr"/>
+      <c r="AIY1" t="inlineStr"/>
+      <c r="AIZ1" t="inlineStr"/>
+      <c r="AJA1" t="inlineStr"/>
+      <c r="AJB1" t="inlineStr"/>
+      <c r="AJC1" t="inlineStr"/>
+      <c r="AJD1" t="inlineStr"/>
+      <c r="AJE1" t="inlineStr"/>
+      <c r="AJF1" t="inlineStr"/>
+      <c r="AJG1" t="inlineStr"/>
+      <c r="AJH1" t="inlineStr"/>
+      <c r="AJI1" t="inlineStr"/>
+      <c r="AJJ1" t="inlineStr"/>
+      <c r="AJK1" t="inlineStr"/>
+      <c r="AJL1" t="inlineStr"/>
+      <c r="AJM1" t="inlineStr"/>
+      <c r="AJN1" t="inlineStr"/>
+      <c r="AJO1" t="inlineStr"/>
+      <c r="AJP1" t="inlineStr"/>
+      <c r="AJQ1" t="inlineStr"/>
+      <c r="AJR1" t="inlineStr"/>
+      <c r="AJS1" t="inlineStr"/>
+      <c r="AJT1" t="inlineStr"/>
+      <c r="AJU1" t="inlineStr"/>
+      <c r="AJV1" t="inlineStr"/>
+      <c r="AJW1" t="inlineStr"/>
+      <c r="AJX1" t="inlineStr"/>
+      <c r="AJY1" t="inlineStr"/>
+      <c r="AJZ1" t="inlineStr"/>
+      <c r="AKA1" t="inlineStr"/>
+      <c r="AKB1" t="inlineStr"/>
+      <c r="AKC1" t="inlineStr"/>
+      <c r="AKD1" t="inlineStr"/>
+      <c r="AKE1" t="inlineStr"/>
+      <c r="AKF1" t="inlineStr"/>
+      <c r="AKG1" t="inlineStr"/>
+      <c r="AKH1" t="inlineStr"/>
+      <c r="AKI1" t="inlineStr"/>
+      <c r="AKJ1" t="inlineStr"/>
+      <c r="AKK1" t="inlineStr"/>
+      <c r="AKL1" t="inlineStr"/>
+      <c r="AKM1" t="inlineStr"/>
+      <c r="AKN1" t="inlineStr"/>
+      <c r="AKO1" t="inlineStr"/>
+      <c r="AKP1" t="inlineStr"/>
+      <c r="AKQ1" t="inlineStr"/>
+      <c r="AKR1" t="inlineStr"/>
+      <c r="AKS1" t="inlineStr"/>
+      <c r="AKT1" t="inlineStr"/>
+      <c r="AKU1" t="inlineStr"/>
+      <c r="AKV1" t="inlineStr"/>
+      <c r="AKW1" t="inlineStr"/>
+      <c r="AKX1" t="inlineStr"/>
+      <c r="AKY1" t="inlineStr"/>
+      <c r="AKZ1" t="inlineStr"/>
+      <c r="ALA1" t="inlineStr"/>
+      <c r="ALB1" t="inlineStr"/>
+      <c r="ALC1" t="inlineStr"/>
+      <c r="ALD1" t="inlineStr"/>
+      <c r="ALE1" t="inlineStr"/>
+      <c r="ALF1" t="inlineStr"/>
+      <c r="ALG1" t="inlineStr"/>
+      <c r="ALH1" t="inlineStr"/>
+      <c r="ALI1" t="inlineStr"/>
+      <c r="ALJ1" t="inlineStr"/>
+      <c r="ALK1" t="inlineStr"/>
+      <c r="ALL1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1049987</v>
+      </c>
+      <c r="B2" t="n">
+        <v>172012</v>
+      </c>
+      <c r="C2" t="n">
+        <v>590165</v>
+      </c>
+      <c r="D2" t="n">
+        <v>191507</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38433</v>
+      </c>
+      <c r="F2" t="n">
+        <v>620364</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000624</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4026</v>
+      </c>
+      <c r="I2" t="n">
+        <v>282483</v>
+      </c>
+      <c r="J2" t="n">
+        <v>599874</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1171772</v>
+      </c>
+      <c r="L2" t="n">
+        <v>927422</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1189112</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1137020</v>
+      </c>
+      <c r="O2" t="n">
+        <v>974800</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1026421</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>658031</v>
+      </c>
+      <c r="R2" t="n">
+        <v>951104</v>
+      </c>
+      <c r="S2" t="n">
+        <v>170919</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1086084</v>
+      </c>
+      <c r="U2" t="n">
+        <v>107206</v>
+      </c>
+      <c r="V2" t="n">
+        <v>989799</v>
+      </c>
+      <c r="W2" t="n">
+        <v>214959</v>
+      </c>
+      <c r="X2" t="n">
+        <v>120686</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>260183</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>341772</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>593484</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>427106</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>84869</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1242</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>152191</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1062747</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>137108</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>877342</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>183755</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>925478</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>387435</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>134566</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1070862</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>963054</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>131635</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>533142</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>894747</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2674</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>632013</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1016749</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>949537</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>218849</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>556908</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>179016</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>698661</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>281291</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1193619</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>484194</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>628187</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1161049</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>537361</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>39839</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3117</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1075483</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>429589</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>162272</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>152529</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1191952</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>652673</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>568825</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>621534</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>212325</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>884113</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>770660</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>8382</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>399064</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>34847</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>636952</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>529423</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>232110</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>444635</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>595491</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>826288</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>938824</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>783356</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>249732</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>226584</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>808507</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>609402</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1008742</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1031593</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>460428</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>61671</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>290031</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>916481</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>253252</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>115346</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1008276</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>72167</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>249751</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>163594</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>43598</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1059449</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>720329</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>655780</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>743066</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>508080</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1197944</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>704278</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>50803</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>795635</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>754117</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>336811</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>496373</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>97017</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>335391</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>730332</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>848232</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>464966</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>340172</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>681593</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>301623</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>143619</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1153600</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>410449</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>623951</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>990782</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1173869</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1018510</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>803504</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>466895</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>182063</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>212493</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>495673</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>541599</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>700083</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>783858</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>80376</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>813387</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>8268</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1073547</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>26990</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>261310</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>776233</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>170577</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>532784</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>721787</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>460249</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>968662</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>82425</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1122475</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>871649</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>984640</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>612283</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>522800</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>727019</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>853401</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>866214</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>857217</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>227736</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>262588</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>825692</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1148400</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1131736</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>648074</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>696850</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>242586</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>173036</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>436861</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>766214</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>1098329</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>820148</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>761706</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>235134</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1034088</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>1186439</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>857915</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>872838</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>39837</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>254439</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>507258</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>1029420</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>1101567</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>1174617</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>663849</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>400472</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>685921</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>416504</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>707898</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>149210</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>297158</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>18931</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>893356</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>393060</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>127410</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>1141137</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>987190</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>185845</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>892542</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>970290</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>356502</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>230801</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>587015</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>45784</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>313978</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>390833</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>729359</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>907154</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>919562</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>683592</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>1186144</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>23062</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>351309</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>118502</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>1129035</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>280589</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>763241</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>268210</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>492570</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>712065</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>320936</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>352225</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>947031</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>535710</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>322442</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>779049</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>741268</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>963855</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>380606</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>316913</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>116648</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>805352</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>626183</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>662726</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>89114</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>942291</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>957007</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>25381</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>245309</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>724171</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>1098976</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>867317</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>561167</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>699995</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>44580</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>922108</v>
+      </c>
+      <c r="II2" t="n">
+        <v>600482</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>760159</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>677616</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>980385</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>911677</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>157233</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>175151</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>747461</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>280123</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>420202</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>954602</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>247527</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>822978</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>330196</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>822788</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>758533</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>457047</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>404586</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>1035750</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>519287</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>931917</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>303131</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>489814</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>675633</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>328442</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>1184412</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>644260</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>1031606</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1103754</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>560231</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>969257</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>1155963</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>629554</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>1094794</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>1146395</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>306598</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>142046</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>359912</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>739451</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>201390</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>810214</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>1060244</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>1213696</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>359624</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>995205</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>203330</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>474339</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>431881</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>831402</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>47241</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>672371</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>425632</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>1182417</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>327762</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>128708</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>475958</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>1066062</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>1041271</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>639123</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>384788</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>1124214</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>656961</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>418479</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>403612</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>388984</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>481711</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>446521</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>362002</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>827756</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>1066697</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>302704</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>1006382</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>1014390</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>153403</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>88778</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>33961</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>166041</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>1117762</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>580315</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>484226</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>203705</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>595733</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>582914</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>1214460</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>675422</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>1013310</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>909529</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>345436</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>948898</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>30165</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>706793</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>1045553</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>394788</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>1158992</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>101653</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>511517</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>1020477</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>246744</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>997986</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>441471</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>186807</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>289464</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>404005</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>866626</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>749709</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>912617</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>873287</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>138361</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>178144</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>1008675</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>154466</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>354531</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>1065281</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>535075</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>787001</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>716613</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>933265</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>973127</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>868230</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>95382</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>17778</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>103321</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>32065</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>286326</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>992609</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>903346</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>960581</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>487820</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>423996</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>225651</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>1120866</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>381572</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>87022</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>834910</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>25387</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>58258</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>273961</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>977677</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>1163317</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>191011</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>676604</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>69948</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>1200643</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>680974</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>337696</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>16752</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>36492</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>374268</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>10907</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>815152</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>1132740</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>1072871</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>720443</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>649882</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>486721</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>141621</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>863890</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>461719</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>1147392</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>1202442</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>845874</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>625768</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>1047871</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>1022514</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>275721</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>122165</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>273033</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>930456</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>695186</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>359137</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>1167195</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>690603</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>254630</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>683651</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>64066</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>899001</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>921520</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>468709</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>436286</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>609792</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>542608</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>840613</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>554969</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>566248</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>260274</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>1025716</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>81711</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>744380</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>756658</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>180036</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>477853</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>539246</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>392176</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>139943</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>149502</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>867</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>20298</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>354242</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>679506</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>176048</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>615358</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>883396</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>702929</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>1170658</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>667189</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>651238</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>184628</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>1040068</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>640069</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>780024</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>581124</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>781666</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>29067</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>131312</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>319743</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>829206</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>373060</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>794539</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>194866</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>11901</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>293379</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>239057</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>386421</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>634962</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>505155</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>945681</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>100496</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>16461</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>106402</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>22056</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>308229</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>348658</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>1090372</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>770098</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>1164762</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>332120</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>201883</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>470942</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>521544</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>51345</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>223458</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>1003149</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>385702</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>13948</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>855681</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>946989</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>771185</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>431394</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>500329</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>166850</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>963717</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>312463</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>1079531</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>656014</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>1011962</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>197153</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>337594</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>586476</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>591430</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>1109766</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>1037859</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1135743</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>1020261</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>898204</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>1108059</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>397349</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>645962</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>10586</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>114660</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>371981</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>838613</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>159390</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>845786</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>434800</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>531188</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>663037</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>526979</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>139907</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>4831</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>811198</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>777373</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>641955</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>752719</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>299697</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>980985</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>584554</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>37725</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>15207</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>1119343</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>901716</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>1030547</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>861938</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>846040</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>12367</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>537553</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>1054682</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>719498</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>1042525</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>370290</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>411108</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>346370</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>1092930</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>307961</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>144434</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>567809</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>498834</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>669647</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>77421</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>214955</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>1176654</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>765522</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>1076398</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>263414</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>68586</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>734700</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>54970</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>1114234</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>123731</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>688902</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>993696</v>
+      </c>
+      <c r="US2" t="n">
+        <v>368549</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>850735</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>220910</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>735292</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>1137615</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>113072</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>958621</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>806607</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>588054</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>604817</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>689686</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>401257</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>617878</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>515065</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>406097</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>1005352</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>839766</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>524803</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>538509</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>923746</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>1112873</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>109210</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>978625</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>304622</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>548309</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>572435</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>788325</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>581745</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>83460</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>878465</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>722546</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>292260</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>177940</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>422325</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>693473</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>758641</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>314760</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>887453</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>239481</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>519733</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>630544</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>155477</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>91710</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>222111</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>565629</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>229564</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>293057</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>732420</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>562288</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>571237</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>91847</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>1183620</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>196090</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>521136</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>301516</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>512508</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>832544</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>898095</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>99095</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>256729</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>820655</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>509015</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>740954</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>704691</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>940384</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>481508</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>551434</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>269680</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>12405</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>614248</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>924661</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>228590</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>574600</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>1156771</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>297765</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>79296</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>968466</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>428377</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>197465</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>528881</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>514081</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>800297</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>661413</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>845103</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>577311</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>1070534</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>440303</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>1125976</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>340780</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>1218271</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>21298</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>909842</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>340110</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>491985</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>78588</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>886526</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>290182</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1123369</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>934980</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>106708</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>1197002</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>325319</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>114741</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>855820</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>1143779</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1055130</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>418349</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>590709</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>1149913</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>1091984</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>411993</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>476267</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>110406</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>66738</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>601203</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>556058</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>365820</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>53291</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>843606</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>125909</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>586032</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>438896</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>616013</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>1097536</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>64364</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>208652</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>543691</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>1209355</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>551491</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>1221030</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>320034</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>493771</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>996910</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>487494</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>398324</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>393433</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>150848</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>345122</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>928837</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>554881</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>942730</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>1001452</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>750918</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>880659</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>626508</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>433838</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>251040</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>1084978</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>1056800</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>322002</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>221108</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>274443</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>783910</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>1127075</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>606670</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>999188</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>1190748</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>168501</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>738416</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>527942</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>500979</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>238691</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>1053304</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>1208416</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>6497</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>504333</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>824508</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>1191850</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>832525</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>791609</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>702999</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>861076</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>459315</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>820293</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>1152034</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>768672</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>597734</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>732840</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>69191</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>605664</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>751957</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>234968</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>792389</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>327603</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>1131987</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>847854</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>188320</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>456814</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>237604</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>691627</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>239477</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>352812</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>206178</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>426460</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>549918</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>95792</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>452503</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>1027206</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>1202852</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>502134</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>277727</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>712013</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>49585</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>725191</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>787678</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>71321</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>709333</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>159787</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>798657</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>285251</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>1087445</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>621342</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>217781</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>1112482</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>311746</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>146022</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>907766</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>1180165</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>654744</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>270236</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>986138</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>1111349</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>86997</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>443116</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>100921</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>94311</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>671306</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>1103808</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>159607</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>544051</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>1078650</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>366717</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>276383</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>802550</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>445066</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>530753</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>192264</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>860820</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>468731</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>1169600</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>285649</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>370047</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>601952</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>735983</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>574141</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>885462</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>471745</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>838453</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>865347</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>432804</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>667973</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>851743</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>298224</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>451584</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>965338</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>943404</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>1165821</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>233587</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>105051</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>185665</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>1044284</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>881251</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>378603</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>74854</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>465766</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>644973</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>972731</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>32386</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>435729</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>202905</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>135039</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>976484</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>41318</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>773595</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>52544</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>1143682</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>800413</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>573948</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>132832</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>448645</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>957123</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>365241</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>931079</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>257664</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>1139696</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>815678</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>1108716</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>486222</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>23685</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>1105093</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>890522</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>413921</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>686880</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>257472</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>377037</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>936856</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>1158382</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>988166</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>28209</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>1076489</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>522788</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>244185</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>443818</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>218117</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>1199543</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>1023306</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>876039</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>1082813</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>756400</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>28149</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>816500</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>603712</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>415050</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>679861</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>333025</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>1115721</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>423614</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>1046318</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>356243</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>573172</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>478113</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>183547</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>109702</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>834762</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>75940</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>279363</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>482850</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>72688</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>455870</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>1035792</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>1081068</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>376086</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>89731</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>935107</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>1071157</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>952753</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>886841</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>164426</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>409316</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>790322</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>194003</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>389860</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>453295</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>621106</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>716768</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>93781</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>462282</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>1207928</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>265947</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>379908</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>906891</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>1204657</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>725883</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>697760</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>1133665</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>60635</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>515857</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>1053159</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>774864</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>607096</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>668700</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>309990</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>1141300</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>380128</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>860628</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>761405</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>762401</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>991326</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>247572</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>889580</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>1062426</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>1082574</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>359193</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>918668</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>547171</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>1178265</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>325480</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>747315</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>1016500</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>57802</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>1107826</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>1097284</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>614249</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>267840</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>197731</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>7849</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>1196639</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>48604</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>119776</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>349741</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>65367</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>659099</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>166665</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>1161326</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>593055</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>1039018</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>804803</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>714871</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>983763</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>447501</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>102678</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>1092962</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>952912</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>1095332</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>636113</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>208221</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>633350</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>795173</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>495341</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>894955</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>714977</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>578525</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>558841</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>333989</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>499370</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>1067966</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>163394</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1210142</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>246</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>709410</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>5507</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>1004105</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>513980</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>638556</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>209952</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>773641</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>123399</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>55521</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>479335</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>642496</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>450576</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>408085</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>916160</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>900960</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>569947</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>914420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -844,14 +5843,6 @@
       <c r="B1" t="n">
         <v>25</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -883,6 +5874,330 @@
       </c>
       <c r="J2" t="n">
         <v>876</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6443056</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3601565</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>62468</v>
+      </c>
+      <c r="B2" t="n">
+        <v>110345</v>
+      </c>
+      <c r="C2" t="n">
+        <v>51197</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35762</v>
+      </c>
+      <c r="E2" t="n">
+        <v>54264</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12790</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44851</v>
+      </c>
+      <c r="H2" t="n">
+        <v>123380</v>
+      </c>
+      <c r="I2" t="n">
+        <v>72626</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33455</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19795</v>
+      </c>
+      <c r="L2" t="n">
+        <v>18486</v>
+      </c>
+      <c r="M2" t="n">
+        <v>94301</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5971</v>
+      </c>
+      <c r="O2" t="n">
+        <v>79462</v>
+      </c>
+      <c r="P2" t="n">
+        <v>21492</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>33723</v>
+      </c>
+      <c r="R2" t="n">
+        <v>15431</v>
+      </c>
+      <c r="S2" t="n">
+        <v>61177</v>
+      </c>
+      <c r="T2" t="n">
+        <v>41491</v>
+      </c>
+      <c r="U2" t="n">
+        <v>87463</v>
+      </c>
+      <c r="V2" t="n">
+        <v>100543</v>
+      </c>
+      <c r="W2" t="n">
+        <v>5207</v>
+      </c>
+      <c r="X2" t="n">
+        <v>121139</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>25181</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>118731</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>77563</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>82577</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>34829</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>30651</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>10065</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>80319</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>59694</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>113510</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>25362</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>75980</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>933</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>65122</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>58450</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>92932</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>85632</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>56797</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>47545</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>105294</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6699</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>89176</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>83536</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>121633</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>72186</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>39368</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>103937</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>97848</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>96261</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>31396</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>107369</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>45555</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>115299</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>50826</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>104140</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>128775</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>61011</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>127310</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>92037</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>75250</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>117373</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>71761</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>10360</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>111475</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>8807</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4476</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>39930</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>70037</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>13628</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>108502</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>68039</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>14713</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>45452</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>42731</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>100268</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>53117</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>49132</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>21220</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>130180</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>28920</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>68653</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>76262</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>65541</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>28026</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>18436</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>86803</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>58400</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>24498</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>23410</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>119255</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>38642</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>14507</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_NEH(InsertionUPMixedImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(InsertionUPMixedImprovement).xlsx
@@ -20,6 +20,7 @@
     <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="tai_j1000_m10_1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="tai_j1000_m10_1r" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1448,6 +1449,3030 @@
       </c>
       <c r="B1" t="n">
         <v>3947240</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1049987</v>
+      </c>
+      <c r="B2" t="n">
+        <v>172012</v>
+      </c>
+      <c r="C2" t="n">
+        <v>590165</v>
+      </c>
+      <c r="D2" t="n">
+        <v>191507</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38433</v>
+      </c>
+      <c r="F2" t="n">
+        <v>620364</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000624</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4026</v>
+      </c>
+      <c r="I2" t="n">
+        <v>282483</v>
+      </c>
+      <c r="J2" t="n">
+        <v>599874</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1171772</v>
+      </c>
+      <c r="L2" t="n">
+        <v>927422</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1189112</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1137020</v>
+      </c>
+      <c r="O2" t="n">
+        <v>974800</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1026421</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>658031</v>
+      </c>
+      <c r="R2" t="n">
+        <v>951104</v>
+      </c>
+      <c r="S2" t="n">
+        <v>170919</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1086084</v>
+      </c>
+      <c r="U2" t="n">
+        <v>107206</v>
+      </c>
+      <c r="V2" t="n">
+        <v>989799</v>
+      </c>
+      <c r="W2" t="n">
+        <v>214959</v>
+      </c>
+      <c r="X2" t="n">
+        <v>120686</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>260183</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>341772</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>593484</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>427106</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>84869</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1242</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>152191</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1062747</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>137108</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>877342</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>183755</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>925478</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>387435</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>134566</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1070862</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>963054</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>131635</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>533142</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>894747</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2674</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>632013</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1016749</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>949537</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>218849</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>556908</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>179016</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>698661</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>281291</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1193619</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>484194</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>628187</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1161049</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>537361</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>39839</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3117</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1075483</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>429589</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>162272</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>152529</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1191952</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>652673</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>568825</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>621534</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>212325</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>884113</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>770660</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>8382</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>399064</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>34847</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>636952</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>529423</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>232110</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>444635</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>595491</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>826288</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>938824</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>783356</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>249732</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>226584</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>808507</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>609402</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1008742</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1031593</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>460428</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>61671</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>290031</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>916481</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>253252</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>115346</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1008276</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>72167</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>249751</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>163594</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>43598</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1059449</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>720329</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>655780</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>743066</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>508080</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1197944</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>704278</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>50803</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>795635</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>754117</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>336811</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>496373</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>97017</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>335391</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>730332</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>848232</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>464966</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>340172</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>681593</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>301623</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>143619</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1153600</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>410449</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>623951</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>990782</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1173869</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1018510</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>803504</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>466895</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>182063</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>212493</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>495673</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>541599</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>700083</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>783858</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>80376</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>813387</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>8268</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1073547</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>26990</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>261310</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>776233</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>170577</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>532784</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>721787</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>460249</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>968662</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>82425</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1122475</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>871649</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>984640</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>612283</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>522800</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>727019</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>853401</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>866214</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>857217</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>227736</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>262588</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>825692</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1148400</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1131736</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>648074</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>696850</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>242586</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>173036</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>436861</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>766214</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>1098329</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>820148</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>761706</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>235134</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1034088</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>1186439</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>857915</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>872838</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>39837</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>254439</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>507258</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>1029420</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>1101567</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>1174617</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>663849</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>400472</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>685921</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>416504</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>707898</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>149210</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>297158</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>18931</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>893356</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>393060</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>127410</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>1141137</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>987190</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>185845</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>892542</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>970290</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>356502</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>230801</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>587015</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>45784</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>313978</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>390833</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>729359</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>907154</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>919562</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>683592</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>1186144</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>23062</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>351309</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>118502</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>1129035</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>280589</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>763241</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>268210</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>492570</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>712065</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>320936</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>352225</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>947031</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>535710</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>322442</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>779049</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>741268</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>963855</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>380606</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>316913</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>116648</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>805352</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>626183</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>662726</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>89114</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>942291</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>957007</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>25381</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>245309</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>724171</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>1098976</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>867317</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>561167</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>699995</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>44580</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>922108</v>
+      </c>
+      <c r="II2" t="n">
+        <v>600482</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>760159</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>677616</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>980385</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>911677</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>157233</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>175151</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>747461</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>280123</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>420202</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>954602</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>247527</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>822978</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>330196</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>822788</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>758533</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>457047</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>404586</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>1035750</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>519287</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>931917</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>303131</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>489814</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>675633</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>328442</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>1184412</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>644260</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>1031606</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1103754</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>560231</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>969257</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>1155963</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>629554</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>1094794</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>1146395</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>306598</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>142046</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>359912</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>739451</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>201390</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>810214</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>1060244</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>1213696</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>359624</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>995205</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>203330</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>474339</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>431881</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>831402</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>47241</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>672371</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>425632</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>1182417</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>327762</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>128708</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>475958</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>1066062</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>1041271</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>639123</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>384788</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>1124214</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>656961</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>418479</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>403612</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>388984</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>481711</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>446521</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>362002</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>827756</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>1066697</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>302704</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>1006382</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>1014390</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>153403</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>88778</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>33961</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>166041</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>1117762</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>580315</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>484226</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>203705</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>595733</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>582914</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>1214460</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>675422</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>1013310</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>909529</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>345436</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>948898</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>30165</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>706793</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>1045553</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>394788</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>1158992</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>101653</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>511517</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>1020477</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>246744</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>997986</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>441471</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>186807</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>289464</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>404005</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>866626</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>749709</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>912617</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>873287</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>138361</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>178144</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>1008675</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>154466</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>354531</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>1065281</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>535075</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>787001</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>716613</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>933265</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>973127</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>868230</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>95382</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>17778</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>103321</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>32065</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>286326</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>992609</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>903346</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>960581</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>487820</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>423996</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>225651</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>1120866</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>381572</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>87022</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>834910</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>25387</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>58258</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>273961</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>977677</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>1163317</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>191011</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>676604</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>69948</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>1200643</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>680974</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>337696</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>16752</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>36492</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>374268</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>10907</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>815152</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>1132740</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>1072871</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>720443</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>649882</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>486721</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>141621</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>863890</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>461719</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>1147392</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>1202442</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>845874</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>625768</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>1047871</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>1022514</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>275721</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>122165</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>273033</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>930456</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>695186</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>359137</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>1167195</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>690603</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>254630</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>683651</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>64066</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>899001</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>921520</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>468709</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>436286</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>609792</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>542608</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>840613</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>554969</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>566248</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>260274</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>1025716</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>81711</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>744380</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>756658</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>180036</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>477853</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>539246</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>392176</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>139943</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>149502</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>867</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>20298</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>354242</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>679506</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>176048</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>615358</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>883396</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>702929</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>1170658</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>667189</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>651238</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>184628</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>1040068</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>640069</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>780024</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>581124</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>781666</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>29067</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>131312</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>319743</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>829206</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>373060</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>794539</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>194866</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>11901</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>293379</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>239057</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>386421</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>634962</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>505155</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>945681</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>100496</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>16461</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>106402</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>22056</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>308229</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>348658</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>1090372</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>770098</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>1164762</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>332120</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>201883</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>470942</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>521544</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>51345</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>223458</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>1003149</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>385702</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>13948</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>855681</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>946989</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>771185</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>431394</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>500329</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>166850</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>963717</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>312463</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>1079531</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>656014</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>1011962</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>197153</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>337594</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>586476</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>591430</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>1109766</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>1037859</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1135743</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>1020261</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>898204</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>1108059</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>397349</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>645962</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>10586</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>114660</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>371981</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>838613</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>159390</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>845786</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>434800</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>531188</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>663037</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>526979</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>139907</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>4831</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>811198</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>777373</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>641955</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>752719</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>299697</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>980985</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>584554</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>37725</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>15207</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>1119343</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>901716</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>1030547</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>861938</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>846040</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>12367</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>537553</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>1054682</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>719498</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>1042525</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>370290</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>411108</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>346370</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>1092930</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>307961</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>144434</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>567809</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>498834</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>669647</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>77421</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>214955</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>1176654</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>765522</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>1076398</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>263414</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>68586</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>734700</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>54970</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>1114234</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>123731</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>688902</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>993696</v>
+      </c>
+      <c r="US2" t="n">
+        <v>368549</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>850735</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>220910</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>735292</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>1137615</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>113072</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>958621</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>806607</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>588054</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>604817</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>689686</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>401257</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>617878</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>515065</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>406097</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>1005352</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>839766</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>524803</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>538509</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>923746</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>1112873</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>109210</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>978625</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>304622</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>548309</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>572435</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>788325</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>581745</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>83460</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>878465</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>722546</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>292260</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>177940</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>422325</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>693473</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>758641</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>314760</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>887453</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>239481</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>519733</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>630544</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>155477</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>91710</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>222111</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>565629</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>229564</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>293057</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>732420</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>562288</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>571237</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>91847</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>1183620</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>196090</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>521136</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>301516</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>512508</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>832544</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>898095</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>99095</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>256729</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>820655</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>509015</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>740954</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>704691</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>940384</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>481508</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>551434</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>269680</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>12405</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>614248</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>924661</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>228590</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>574600</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>1156771</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>297765</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>79296</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>968466</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>428377</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>197465</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>528881</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>514081</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>800297</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>661413</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>845103</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>577311</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>1070534</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>440303</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>1125976</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>340780</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>1218271</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>21298</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>909842</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>340110</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>491985</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>78588</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>886526</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>290182</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1123369</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>934980</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>106708</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>1197002</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>325319</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>114741</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>855820</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>1143779</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1055130</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>418349</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>590709</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>1149913</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>1091984</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>411993</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>476267</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>110406</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>66738</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>601203</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>556058</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>365820</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>53291</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>843606</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>125909</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>586032</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>438896</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>616013</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>1097536</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>64364</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>208652</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>543691</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>1209355</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>551491</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>1221030</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>320034</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>493771</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>996910</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>487494</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>398324</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>393433</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>150848</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>345122</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>928837</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>554881</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>942730</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>1001452</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>750918</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>880659</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>626508</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>433838</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>251040</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>1084978</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>1056800</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>322002</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>221108</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>274443</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>783910</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>1127075</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>606670</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>999188</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>1190748</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>168501</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>738416</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>527942</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>500979</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>238691</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>1053304</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>1208416</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>6497</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>504333</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>824508</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>1191850</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>832525</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>791609</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>702999</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>861076</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>459315</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>820293</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>1152034</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>768672</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>597734</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>732840</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>69191</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>605664</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>751957</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>234968</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>792389</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>327603</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>1131987</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>847854</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>188320</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>456814</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>237604</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>691627</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>239477</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>352812</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>206178</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>426460</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>549918</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>95792</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>452503</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>1027206</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>1202852</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>502134</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>277727</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>712013</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>49585</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>725191</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>787678</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>71321</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>709333</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>159787</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>798657</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>285251</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>1087445</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>621342</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>217781</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>1112482</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>311746</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>146022</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>907766</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>1180165</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>654744</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>270236</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>986138</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>1111349</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>86997</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>443116</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>100921</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>94311</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>671306</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>1103808</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>159607</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>544051</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>1078650</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>366717</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>276383</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>802550</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>445066</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>530753</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>192264</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>860820</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>468731</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>1169600</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>285649</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>370047</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>601952</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>735983</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>574141</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>885462</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>471745</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>838453</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>865347</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>432804</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>667973</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>851743</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>298224</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>451584</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>965338</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>943404</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>1165821</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>233587</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>105051</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>185665</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>1044284</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>881251</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>378603</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>74854</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>465766</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>644973</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>972731</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>32386</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>435729</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>202905</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>135039</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>976484</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>41318</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>773595</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>52544</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>1143682</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>800413</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>573948</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>132832</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>448645</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>957123</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>365241</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>931079</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>257664</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>1139696</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>815678</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>1108716</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>486222</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>23685</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>1105093</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>890522</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>413921</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>686880</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>257472</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>377037</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>936856</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>1158382</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>988166</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>28209</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>1076489</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>522788</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>244185</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>443818</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>218117</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>1199543</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>1023306</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>876039</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>1082813</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>756400</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>28149</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>816500</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>603712</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>415050</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>679861</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>333025</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>1115721</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>423614</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>1046318</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>356243</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>573172</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>478113</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>183547</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>109702</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>834762</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>75940</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>279363</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>482850</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>72688</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>455870</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>1035792</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>1081068</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>376086</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>89731</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>935107</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>1071157</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>952753</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>886841</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>164426</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>409316</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>790322</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>194003</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>389860</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>453295</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>621106</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>716768</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>93781</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>462282</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>1207928</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>265947</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>379908</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>906891</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>1204657</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>725883</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>697760</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>1133665</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>60635</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>515857</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>1053159</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>774864</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>607096</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>668700</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>309990</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>1141300</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>380128</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>860628</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>761405</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>762401</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>991326</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>247572</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>889580</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>1062426</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>1082574</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>359193</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>918668</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>547171</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>1178265</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>325480</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>747315</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>1016500</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>57802</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>1107826</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>1097284</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>614249</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>267840</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>197731</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>7849</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>1196639</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>48604</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>119776</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>349741</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>65367</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>659099</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>166665</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>1161326</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>593055</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>1039018</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>804803</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>714871</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>983763</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>447501</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>102678</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>1092962</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>952912</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>1095332</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>636113</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>208221</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>633350</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>795173</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>495341</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>894955</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>714977</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>578525</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>558841</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>333989</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>499370</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>1067966</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>163394</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1210142</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>246</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>709410</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>5507</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>1004105</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>513980</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>638556</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>209952</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>773641</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>123399</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>55521</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>479335</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>642496</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>450576</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>408085</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>916160</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>900960</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>569947</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>914420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>576683357</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3822300</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -2450,3004 +5475,3004 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1049987</v>
+        <v>1159995</v>
       </c>
       <c r="B2" t="n">
-        <v>172012</v>
+        <v>1049241</v>
       </c>
       <c r="C2" t="n">
-        <v>590165</v>
+        <v>538366</v>
       </c>
       <c r="D2" t="n">
-        <v>191507</v>
+        <v>1215711</v>
       </c>
       <c r="E2" t="n">
-        <v>38433</v>
+        <v>854549</v>
       </c>
       <c r="F2" t="n">
-        <v>620364</v>
+        <v>639580</v>
       </c>
       <c r="G2" t="n">
-        <v>1000624</v>
+        <v>1004720</v>
       </c>
       <c r="H2" t="n">
-        <v>4026</v>
+        <v>151444</v>
       </c>
       <c r="I2" t="n">
-        <v>282483</v>
+        <v>904860</v>
       </c>
       <c r="J2" t="n">
-        <v>599874</v>
+        <v>321187</v>
       </c>
       <c r="K2" t="n">
-        <v>1171772</v>
+        <v>332223</v>
       </c>
       <c r="L2" t="n">
-        <v>927422</v>
+        <v>882422</v>
       </c>
       <c r="M2" t="n">
-        <v>1189112</v>
+        <v>655464</v>
       </c>
       <c r="N2" t="n">
-        <v>1137020</v>
+        <v>1068822</v>
       </c>
       <c r="O2" t="n">
-        <v>974800</v>
+        <v>648743</v>
       </c>
       <c r="P2" t="n">
-        <v>1026421</v>
+        <v>1113463</v>
       </c>
       <c r="Q2" t="n">
-        <v>658031</v>
+        <v>591448</v>
       </c>
       <c r="R2" t="n">
-        <v>951104</v>
+        <v>667016</v>
       </c>
       <c r="S2" t="n">
-        <v>170919</v>
+        <v>460579</v>
       </c>
       <c r="T2" t="n">
-        <v>1086084</v>
+        <v>821464</v>
       </c>
       <c r="U2" t="n">
-        <v>107206</v>
+        <v>464322</v>
       </c>
       <c r="V2" t="n">
-        <v>989799</v>
+        <v>350449</v>
       </c>
       <c r="W2" t="n">
-        <v>214959</v>
+        <v>180882</v>
       </c>
       <c r="X2" t="n">
-        <v>120686</v>
+        <v>632722</v>
       </c>
       <c r="Y2" t="n">
-        <v>260183</v>
+        <v>881828</v>
       </c>
       <c r="Z2" t="n">
-        <v>341772</v>
+        <v>785986</v>
       </c>
       <c r="AA2" t="n">
-        <v>593484</v>
+        <v>756447</v>
       </c>
       <c r="AB2" t="n">
-        <v>427106</v>
+        <v>109498</v>
       </c>
       <c r="AC2" t="n">
-        <v>84869</v>
+        <v>700602</v>
       </c>
       <c r="AD2" t="n">
-        <v>1242</v>
+        <v>688409</v>
       </c>
       <c r="AE2" t="n">
-        <v>152191</v>
+        <v>426671</v>
       </c>
       <c r="AF2" t="n">
-        <v>1062747</v>
+        <v>292301</v>
       </c>
       <c r="AG2" t="n">
-        <v>137108</v>
+        <v>372766</v>
       </c>
       <c r="AH2" t="n">
-        <v>877342</v>
+        <v>866767</v>
       </c>
       <c r="AI2" t="n">
-        <v>183755</v>
+        <v>146639</v>
       </c>
       <c r="AJ2" t="n">
-        <v>925478</v>
+        <v>536400</v>
       </c>
       <c r="AK2" t="n">
-        <v>387435</v>
+        <v>743549</v>
       </c>
       <c r="AL2" t="n">
-        <v>134566</v>
+        <v>330874</v>
       </c>
       <c r="AM2" t="n">
-        <v>1070862</v>
+        <v>495645</v>
       </c>
       <c r="AN2" t="n">
-        <v>963054</v>
+        <v>170174</v>
       </c>
       <c r="AO2" t="n">
-        <v>131635</v>
+        <v>774500</v>
       </c>
       <c r="AP2" t="n">
-        <v>533142</v>
+        <v>253360</v>
       </c>
       <c r="AQ2" t="n">
-        <v>894747</v>
+        <v>349957</v>
       </c>
       <c r="AR2" t="n">
-        <v>2674</v>
+        <v>57904</v>
       </c>
       <c r="AS2" t="n">
-        <v>632013</v>
+        <v>1170955</v>
       </c>
       <c r="AT2" t="n">
-        <v>1016749</v>
+        <v>975998</v>
       </c>
       <c r="AU2" t="n">
-        <v>949537</v>
+        <v>927306</v>
       </c>
       <c r="AV2" t="n">
-        <v>218849</v>
+        <v>401323</v>
       </c>
       <c r="AW2" t="n">
-        <v>556908</v>
+        <v>989240</v>
       </c>
       <c r="AX2" t="n">
-        <v>179016</v>
+        <v>385127</v>
       </c>
       <c r="AY2" t="n">
-        <v>698661</v>
+        <v>369410</v>
       </c>
       <c r="AZ2" t="n">
-        <v>281291</v>
+        <v>433628</v>
       </c>
       <c r="BA2" t="n">
-        <v>1193619</v>
+        <v>710057</v>
       </c>
       <c r="BB2" t="n">
-        <v>484194</v>
+        <v>371443</v>
       </c>
       <c r="BC2" t="n">
-        <v>628187</v>
+        <v>811099</v>
       </c>
       <c r="BD2" t="n">
-        <v>1161049</v>
+        <v>833943</v>
       </c>
       <c r="BE2" t="n">
-        <v>537361</v>
+        <v>647641</v>
       </c>
       <c r="BF2" t="n">
-        <v>39839</v>
+        <v>946213</v>
       </c>
       <c r="BG2" t="n">
-        <v>3117</v>
+        <v>458520</v>
       </c>
       <c r="BH2" t="n">
-        <v>1075483</v>
+        <v>598201</v>
       </c>
       <c r="BI2" t="n">
-        <v>429589</v>
+        <v>393743</v>
       </c>
       <c r="BJ2" t="n">
-        <v>162272</v>
+        <v>261169</v>
       </c>
       <c r="BK2" t="n">
-        <v>152529</v>
+        <v>1209900</v>
       </c>
       <c r="BL2" t="n">
-        <v>1191952</v>
+        <v>127933</v>
       </c>
       <c r="BM2" t="n">
-        <v>652673</v>
+        <v>445559</v>
       </c>
       <c r="BN2" t="n">
-        <v>568825</v>
+        <v>137710</v>
       </c>
       <c r="BO2" t="n">
-        <v>621534</v>
+        <v>167912</v>
       </c>
       <c r="BP2" t="n">
-        <v>212325</v>
+        <v>1015980</v>
       </c>
       <c r="BQ2" t="n">
-        <v>884113</v>
+        <v>172647</v>
       </c>
       <c r="BR2" t="n">
-        <v>770660</v>
+        <v>603946</v>
       </c>
       <c r="BS2" t="n">
-        <v>8382</v>
+        <v>298272</v>
       </c>
       <c r="BT2" t="n">
-        <v>399064</v>
+        <v>1002019</v>
       </c>
       <c r="BU2" t="n">
-        <v>34847</v>
+        <v>516821</v>
       </c>
       <c r="BV2" t="n">
-        <v>636952</v>
+        <v>200417</v>
       </c>
       <c r="BW2" t="n">
-        <v>529423</v>
+        <v>989413</v>
       </c>
       <c r="BX2" t="n">
-        <v>232110</v>
+        <v>523520</v>
       </c>
       <c r="BY2" t="n">
-        <v>444635</v>
+        <v>379187</v>
       </c>
       <c r="BZ2" t="n">
-        <v>595491</v>
+        <v>917350</v>
       </c>
       <c r="CA2" t="n">
-        <v>826288</v>
+        <v>152072</v>
       </c>
       <c r="CB2" t="n">
-        <v>938824</v>
+        <v>479785</v>
       </c>
       <c r="CC2" t="n">
-        <v>783356</v>
+        <v>636909</v>
       </c>
       <c r="CD2" t="n">
-        <v>249732</v>
+        <v>171237</v>
       </c>
       <c r="CE2" t="n">
-        <v>226584</v>
+        <v>737157</v>
       </c>
       <c r="CF2" t="n">
-        <v>808507</v>
+        <v>920120</v>
       </c>
       <c r="CG2" t="n">
-        <v>609402</v>
+        <v>531227</v>
       </c>
       <c r="CH2" t="n">
-        <v>1008742</v>
+        <v>928380</v>
       </c>
       <c r="CI2" t="n">
-        <v>1031593</v>
+        <v>659842</v>
       </c>
       <c r="CJ2" t="n">
-        <v>460428</v>
+        <v>1032577</v>
       </c>
       <c r="CK2" t="n">
-        <v>61671</v>
+        <v>1008075</v>
       </c>
       <c r="CL2" t="n">
-        <v>290031</v>
+        <v>620667</v>
       </c>
       <c r="CM2" t="n">
-        <v>916481</v>
+        <v>508212</v>
       </c>
       <c r="CN2" t="n">
-        <v>253252</v>
+        <v>895121</v>
       </c>
       <c r="CO2" t="n">
-        <v>115346</v>
+        <v>718848</v>
       </c>
       <c r="CP2" t="n">
-        <v>1008276</v>
+        <v>939236</v>
       </c>
       <c r="CQ2" t="n">
-        <v>72167</v>
+        <v>835982</v>
       </c>
       <c r="CR2" t="n">
-        <v>249751</v>
+        <v>779213</v>
       </c>
       <c r="CS2" t="n">
-        <v>163594</v>
+        <v>30550</v>
       </c>
       <c r="CT2" t="n">
-        <v>43598</v>
+        <v>923516</v>
       </c>
       <c r="CU2" t="n">
-        <v>1059449</v>
+        <v>8094</v>
       </c>
       <c r="CV2" t="n">
-        <v>720329</v>
+        <v>848317</v>
       </c>
       <c r="CW2" t="n">
-        <v>655780</v>
+        <v>544721</v>
       </c>
       <c r="CX2" t="n">
-        <v>743066</v>
+        <v>663047</v>
       </c>
       <c r="CY2" t="n">
-        <v>508080</v>
+        <v>859292</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1197944</v>
+        <v>77651</v>
       </c>
       <c r="DA2" t="n">
-        <v>704278</v>
+        <v>1132907</v>
       </c>
       <c r="DB2" t="n">
-        <v>50803</v>
+        <v>131941</v>
       </c>
       <c r="DC2" t="n">
-        <v>795635</v>
+        <v>235878</v>
       </c>
       <c r="DD2" t="n">
-        <v>754117</v>
+        <v>287945</v>
       </c>
       <c r="DE2" t="n">
-        <v>336811</v>
+        <v>108280</v>
       </c>
       <c r="DF2" t="n">
-        <v>496373</v>
+        <v>569180</v>
       </c>
       <c r="DG2" t="n">
-        <v>97017</v>
+        <v>571085</v>
       </c>
       <c r="DH2" t="n">
-        <v>335391</v>
+        <v>609903</v>
       </c>
       <c r="DI2" t="n">
-        <v>730332</v>
+        <v>388216</v>
       </c>
       <c r="DJ2" t="n">
-        <v>848232</v>
+        <v>1030077</v>
       </c>
       <c r="DK2" t="n">
-        <v>464966</v>
+        <v>18146</v>
       </c>
       <c r="DL2" t="n">
-        <v>340172</v>
+        <v>933520</v>
       </c>
       <c r="DM2" t="n">
-        <v>681593</v>
+        <v>411030</v>
       </c>
       <c r="DN2" t="n">
-        <v>301623</v>
+        <v>983543</v>
       </c>
       <c r="DO2" t="n">
-        <v>143619</v>
+        <v>1207115</v>
       </c>
       <c r="DP2" t="n">
-        <v>1153600</v>
+        <v>556716</v>
       </c>
       <c r="DQ2" t="n">
-        <v>410449</v>
+        <v>1103676</v>
       </c>
       <c r="DR2" t="n">
-        <v>623951</v>
+        <v>437918</v>
       </c>
       <c r="DS2" t="n">
-        <v>990782</v>
+        <v>1088550</v>
       </c>
       <c r="DT2" t="n">
-        <v>1173869</v>
+        <v>515175</v>
       </c>
       <c r="DU2" t="n">
-        <v>1018510</v>
+        <v>771993</v>
       </c>
       <c r="DV2" t="n">
-        <v>803504</v>
+        <v>1031924</v>
       </c>
       <c r="DW2" t="n">
-        <v>466895</v>
+        <v>654099</v>
       </c>
       <c r="DX2" t="n">
-        <v>182063</v>
+        <v>1195963</v>
       </c>
       <c r="DY2" t="n">
-        <v>212493</v>
+        <v>524117</v>
       </c>
       <c r="DZ2" t="n">
-        <v>495673</v>
+        <v>1158673</v>
       </c>
       <c r="EA2" t="n">
-        <v>541599</v>
+        <v>898647</v>
       </c>
       <c r="EB2" t="n">
-        <v>700083</v>
+        <v>422462</v>
       </c>
       <c r="EC2" t="n">
-        <v>783858</v>
+        <v>105765</v>
       </c>
       <c r="ED2" t="n">
-        <v>80376</v>
+        <v>92511</v>
       </c>
       <c r="EE2" t="n">
-        <v>813387</v>
+        <v>740968</v>
       </c>
       <c r="EF2" t="n">
-        <v>8268</v>
+        <v>1036814</v>
       </c>
       <c r="EG2" t="n">
-        <v>1073547</v>
+        <v>895290</v>
       </c>
       <c r="EH2" t="n">
-        <v>26990</v>
+        <v>600765</v>
       </c>
       <c r="EI2" t="n">
-        <v>261310</v>
+        <v>1145339</v>
       </c>
       <c r="EJ2" t="n">
-        <v>776233</v>
+        <v>331791</v>
       </c>
       <c r="EK2" t="n">
-        <v>170577</v>
+        <v>211963</v>
       </c>
       <c r="EL2" t="n">
-        <v>532784</v>
+        <v>521979</v>
       </c>
       <c r="EM2" t="n">
-        <v>721787</v>
+        <v>1216474</v>
       </c>
       <c r="EN2" t="n">
-        <v>460249</v>
+        <v>584356</v>
       </c>
       <c r="EO2" t="n">
-        <v>968662</v>
+        <v>962586</v>
       </c>
       <c r="EP2" t="n">
-        <v>82425</v>
+        <v>188077</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1122475</v>
+        <v>14388</v>
       </c>
       <c r="ER2" t="n">
-        <v>871649</v>
+        <v>259475</v>
       </c>
       <c r="ES2" t="n">
-        <v>984640</v>
+        <v>218728</v>
       </c>
       <c r="ET2" t="n">
-        <v>612283</v>
+        <v>168215</v>
       </c>
       <c r="EU2" t="n">
-        <v>522800</v>
+        <v>212496</v>
       </c>
       <c r="EV2" t="n">
-        <v>727019</v>
+        <v>1101722</v>
       </c>
       <c r="EW2" t="n">
-        <v>853401</v>
+        <v>1165975</v>
       </c>
       <c r="EX2" t="n">
-        <v>866214</v>
+        <v>546254</v>
       </c>
       <c r="EY2" t="n">
-        <v>857217</v>
+        <v>966085</v>
       </c>
       <c r="EZ2" t="n">
-        <v>227736</v>
+        <v>661011</v>
       </c>
       <c r="FA2" t="n">
-        <v>262588</v>
+        <v>354686</v>
       </c>
       <c r="FB2" t="n">
-        <v>825692</v>
+        <v>973793</v>
       </c>
       <c r="FC2" t="n">
-        <v>1148400</v>
+        <v>561953</v>
       </c>
       <c r="FD2" t="n">
-        <v>1131736</v>
+        <v>1129679</v>
       </c>
       <c r="FE2" t="n">
-        <v>648074</v>
+        <v>769252</v>
       </c>
       <c r="FF2" t="n">
-        <v>696850</v>
+        <v>942923</v>
       </c>
       <c r="FG2" t="n">
-        <v>242586</v>
+        <v>633233</v>
       </c>
       <c r="FH2" t="n">
-        <v>173036</v>
+        <v>458726</v>
       </c>
       <c r="FI2" t="n">
-        <v>436861</v>
+        <v>321257</v>
       </c>
       <c r="FJ2" t="n">
-        <v>766214</v>
+        <v>22742</v>
       </c>
       <c r="FK2" t="n">
-        <v>1098329</v>
+        <v>393709</v>
       </c>
       <c r="FL2" t="n">
-        <v>820148</v>
+        <v>59609</v>
       </c>
       <c r="FM2" t="n">
-        <v>761706</v>
+        <v>301655</v>
       </c>
       <c r="FN2" t="n">
-        <v>235134</v>
+        <v>4807</v>
       </c>
       <c r="FO2" t="n">
-        <v>1034088</v>
+        <v>40095</v>
       </c>
       <c r="FP2" t="n">
-        <v>1186439</v>
+        <v>837649</v>
       </c>
       <c r="FQ2" t="n">
-        <v>857915</v>
+        <v>357921</v>
       </c>
       <c r="FR2" t="n">
-        <v>872838</v>
+        <v>741259</v>
       </c>
       <c r="FS2" t="n">
-        <v>39837</v>
+        <v>293606</v>
       </c>
       <c r="FT2" t="n">
-        <v>254439</v>
+        <v>878874</v>
       </c>
       <c r="FU2" t="n">
-        <v>507258</v>
+        <v>754419</v>
       </c>
       <c r="FV2" t="n">
-        <v>1029420</v>
+        <v>436682</v>
       </c>
       <c r="FW2" t="n">
-        <v>1101567</v>
+        <v>1198912</v>
       </c>
       <c r="FX2" t="n">
-        <v>1174617</v>
+        <v>921227</v>
       </c>
       <c r="FY2" t="n">
-        <v>663849</v>
+        <v>593454</v>
       </c>
       <c r="FZ2" t="n">
-        <v>400472</v>
+        <v>780654</v>
       </c>
       <c r="GA2" t="n">
-        <v>685921</v>
+        <v>229281</v>
       </c>
       <c r="GB2" t="n">
-        <v>416504</v>
+        <v>96391</v>
       </c>
       <c r="GC2" t="n">
-        <v>707898</v>
+        <v>761655</v>
       </c>
       <c r="GD2" t="n">
-        <v>149210</v>
+        <v>1156032</v>
       </c>
       <c r="GE2" t="n">
-        <v>297158</v>
+        <v>235852</v>
       </c>
       <c r="GF2" t="n">
-        <v>18931</v>
+        <v>587326</v>
       </c>
       <c r="GG2" t="n">
-        <v>893356</v>
+        <v>998585</v>
       </c>
       <c r="GH2" t="n">
-        <v>393060</v>
+        <v>20036</v>
       </c>
       <c r="GI2" t="n">
-        <v>127410</v>
+        <v>481581</v>
       </c>
       <c r="GJ2" t="n">
-        <v>1141137</v>
+        <v>77465</v>
       </c>
       <c r="GK2" t="n">
-        <v>987190</v>
+        <v>963827</v>
       </c>
       <c r="GL2" t="n">
-        <v>185845</v>
+        <v>498940</v>
       </c>
       <c r="GM2" t="n">
-        <v>892542</v>
+        <v>550522</v>
       </c>
       <c r="GN2" t="n">
-        <v>970290</v>
+        <v>939928</v>
       </c>
       <c r="GO2" t="n">
-        <v>356502</v>
+        <v>404133</v>
       </c>
       <c r="GP2" t="n">
-        <v>230801</v>
+        <v>407277</v>
       </c>
       <c r="GQ2" t="n">
-        <v>587015</v>
+        <v>172428</v>
       </c>
       <c r="GR2" t="n">
-        <v>45784</v>
+        <v>121096</v>
       </c>
       <c r="GS2" t="n">
-        <v>313978</v>
+        <v>625679</v>
       </c>
       <c r="GT2" t="n">
-        <v>390833</v>
+        <v>81702</v>
       </c>
       <c r="GU2" t="n">
-        <v>729359</v>
+        <v>270184</v>
       </c>
       <c r="GV2" t="n">
-        <v>907154</v>
+        <v>119032</v>
       </c>
       <c r="GW2" t="n">
-        <v>919562</v>
+        <v>336505</v>
       </c>
       <c r="GX2" t="n">
-        <v>683592</v>
+        <v>913607</v>
       </c>
       <c r="GY2" t="n">
-        <v>1186144</v>
+        <v>757444</v>
       </c>
       <c r="GZ2" t="n">
-        <v>23062</v>
+        <v>140975</v>
       </c>
       <c r="HA2" t="n">
-        <v>351309</v>
+        <v>772444</v>
       </c>
       <c r="HB2" t="n">
-        <v>118502</v>
+        <v>455427</v>
       </c>
       <c r="HC2" t="n">
-        <v>1129035</v>
+        <v>15200</v>
       </c>
       <c r="HD2" t="n">
-        <v>280589</v>
+        <v>861906</v>
       </c>
       <c r="HE2" t="n">
-        <v>763241</v>
+        <v>1132469</v>
       </c>
       <c r="HF2" t="n">
-        <v>268210</v>
+        <v>227721</v>
       </c>
       <c r="HG2" t="n">
-        <v>492570</v>
+        <v>306784</v>
       </c>
       <c r="HH2" t="n">
-        <v>712065</v>
+        <v>574936</v>
       </c>
       <c r="HI2" t="n">
-        <v>320936</v>
+        <v>780393</v>
       </c>
       <c r="HJ2" t="n">
-        <v>352225</v>
+        <v>1189816</v>
       </c>
       <c r="HK2" t="n">
-        <v>947031</v>
+        <v>1010313</v>
       </c>
       <c r="HL2" t="n">
-        <v>535710</v>
+        <v>684113</v>
       </c>
       <c r="HM2" t="n">
-        <v>322442</v>
+        <v>155730</v>
       </c>
       <c r="HN2" t="n">
-        <v>779049</v>
+        <v>599057</v>
       </c>
       <c r="HO2" t="n">
-        <v>741268</v>
+        <v>1225714</v>
       </c>
       <c r="HP2" t="n">
-        <v>963855</v>
+        <v>240580</v>
       </c>
       <c r="HQ2" t="n">
-        <v>380606</v>
+        <v>791086</v>
       </c>
       <c r="HR2" t="n">
-        <v>316913</v>
+        <v>497046</v>
       </c>
       <c r="HS2" t="n">
-        <v>116648</v>
+        <v>573637</v>
       </c>
       <c r="HT2" t="n">
-        <v>805352</v>
+        <v>1049007</v>
       </c>
       <c r="HU2" t="n">
-        <v>626183</v>
+        <v>592106</v>
       </c>
       <c r="HV2" t="n">
-        <v>662726</v>
+        <v>723143</v>
       </c>
       <c r="HW2" t="n">
-        <v>89114</v>
+        <v>806976</v>
       </c>
       <c r="HX2" t="n">
-        <v>942291</v>
+        <v>1149966</v>
       </c>
       <c r="HY2" t="n">
-        <v>957007</v>
+        <v>623113</v>
       </c>
       <c r="HZ2" t="n">
-        <v>25381</v>
+        <v>204713</v>
       </c>
       <c r="IA2" t="n">
-        <v>245309</v>
+        <v>1036077</v>
       </c>
       <c r="IB2" t="n">
-        <v>724171</v>
+        <v>932735</v>
       </c>
       <c r="IC2" t="n">
-        <v>1098976</v>
+        <v>301696</v>
       </c>
       <c r="ID2" t="n">
-        <v>867317</v>
+        <v>338042</v>
       </c>
       <c r="IE2" t="n">
-        <v>561167</v>
+        <v>324079</v>
       </c>
       <c r="IF2" t="n">
-        <v>699995</v>
+        <v>518204</v>
       </c>
       <c r="IG2" t="n">
-        <v>44580</v>
+        <v>0</v>
       </c>
       <c r="IH2" t="n">
-        <v>922108</v>
+        <v>819985</v>
       </c>
       <c r="II2" t="n">
-        <v>600482</v>
+        <v>397519</v>
       </c>
       <c r="IJ2" t="n">
-        <v>760159</v>
+        <v>178130</v>
       </c>
       <c r="IK2" t="n">
-        <v>677616</v>
+        <v>777034</v>
       </c>
       <c r="IL2" t="n">
-        <v>980385</v>
+        <v>87265</v>
       </c>
       <c r="IM2" t="n">
-        <v>911677</v>
+        <v>36720</v>
       </c>
       <c r="IN2" t="n">
-        <v>157233</v>
+        <v>606037</v>
       </c>
       <c r="IO2" t="n">
-        <v>175151</v>
+        <v>454983</v>
       </c>
       <c r="IP2" t="n">
-        <v>747461</v>
+        <v>704140</v>
       </c>
       <c r="IQ2" t="n">
-        <v>280123</v>
+        <v>929763</v>
       </c>
       <c r="IR2" t="n">
-        <v>420202</v>
+        <v>750599</v>
       </c>
       <c r="IS2" t="n">
-        <v>954602</v>
+        <v>1125186</v>
       </c>
       <c r="IT2" t="n">
-        <v>247527</v>
+        <v>426490</v>
       </c>
       <c r="IU2" t="n">
-        <v>822978</v>
+        <v>548369</v>
       </c>
       <c r="IV2" t="n">
-        <v>330196</v>
+        <v>999686</v>
       </c>
       <c r="IW2" t="n">
-        <v>822788</v>
+        <v>55526</v>
       </c>
       <c r="IX2" t="n">
-        <v>758533</v>
+        <v>283360</v>
       </c>
       <c r="IY2" t="n">
-        <v>457047</v>
+        <v>749373</v>
       </c>
       <c r="IZ2" t="n">
-        <v>404586</v>
+        <v>290840</v>
       </c>
       <c r="JA2" t="n">
-        <v>1035750</v>
+        <v>440426</v>
       </c>
       <c r="JB2" t="n">
-        <v>519287</v>
+        <v>204622</v>
       </c>
       <c r="JC2" t="n">
-        <v>931917</v>
+        <v>1232460</v>
       </c>
       <c r="JD2" t="n">
-        <v>303131</v>
+        <v>1119259</v>
       </c>
       <c r="JE2" t="n">
-        <v>489814</v>
+        <v>421917</v>
       </c>
       <c r="JF2" t="n">
-        <v>675633</v>
+        <v>421984</v>
       </c>
       <c r="JG2" t="n">
-        <v>328442</v>
+        <v>183604</v>
       </c>
       <c r="JH2" t="n">
-        <v>1184412</v>
+        <v>430676</v>
       </c>
       <c r="JI2" t="n">
-        <v>644260</v>
+        <v>50823</v>
       </c>
       <c r="JJ2" t="n">
-        <v>1031606</v>
+        <v>374555</v>
       </c>
       <c r="JK2" t="n">
-        <v>1103754</v>
+        <v>1222676</v>
       </c>
       <c r="JL2" t="n">
-        <v>560231</v>
+        <v>287100</v>
       </c>
       <c r="JM2" t="n">
-        <v>969257</v>
+        <v>361826</v>
       </c>
       <c r="JN2" t="n">
-        <v>1155963</v>
+        <v>255176</v>
       </c>
       <c r="JO2" t="n">
-        <v>629554</v>
+        <v>566879</v>
       </c>
       <c r="JP2" t="n">
-        <v>1094794</v>
+        <v>887510</v>
       </c>
       <c r="JQ2" t="n">
-        <v>1146395</v>
+        <v>960379</v>
       </c>
       <c r="JR2" t="n">
-        <v>306598</v>
+        <v>25338</v>
       </c>
       <c r="JS2" t="n">
-        <v>142046</v>
+        <v>889841</v>
       </c>
       <c r="JT2" t="n">
-        <v>359912</v>
+        <v>788769</v>
       </c>
       <c r="JU2" t="n">
-        <v>739451</v>
+        <v>992831</v>
       </c>
       <c r="JV2" t="n">
-        <v>201390</v>
+        <v>456140</v>
       </c>
       <c r="JW2" t="n">
-        <v>810214</v>
+        <v>243433</v>
       </c>
       <c r="JX2" t="n">
-        <v>1060244</v>
+        <v>1068715</v>
       </c>
       <c r="JY2" t="n">
-        <v>1213696</v>
+        <v>676024</v>
       </c>
       <c r="JZ2" t="n">
-        <v>359624</v>
+        <v>875708</v>
       </c>
       <c r="KA2" t="n">
-        <v>995205</v>
+        <v>900439</v>
       </c>
       <c r="KB2" t="n">
-        <v>203330</v>
+        <v>62686</v>
       </c>
       <c r="KC2" t="n">
-        <v>474339</v>
+        <v>483287</v>
       </c>
       <c r="KD2" t="n">
-        <v>431881</v>
+        <v>59798</v>
       </c>
       <c r="KE2" t="n">
-        <v>831402</v>
+        <v>257578</v>
       </c>
       <c r="KF2" t="n">
-        <v>47241</v>
+        <v>1055389</v>
       </c>
       <c r="KG2" t="n">
-        <v>672371</v>
+        <v>363106</v>
       </c>
       <c r="KH2" t="n">
-        <v>425632</v>
+        <v>208610</v>
       </c>
       <c r="KI2" t="n">
-        <v>1182417</v>
+        <v>814101</v>
       </c>
       <c r="KJ2" t="n">
-        <v>327762</v>
+        <v>888971</v>
       </c>
       <c r="KK2" t="n">
-        <v>128708</v>
+        <v>1227808</v>
       </c>
       <c r="KL2" t="n">
-        <v>475958</v>
+        <v>1065088</v>
       </c>
       <c r="KM2" t="n">
-        <v>1066062</v>
+        <v>414205</v>
       </c>
       <c r="KN2" t="n">
-        <v>1041271</v>
+        <v>410233</v>
       </c>
       <c r="KO2" t="n">
-        <v>639123</v>
+        <v>831161</v>
       </c>
       <c r="KP2" t="n">
-        <v>384788</v>
+        <v>1091549</v>
       </c>
       <c r="KQ2" t="n">
-        <v>1124214</v>
+        <v>276280</v>
       </c>
       <c r="KR2" t="n">
-        <v>656961</v>
+        <v>925384</v>
       </c>
       <c r="KS2" t="n">
-        <v>418479</v>
+        <v>157535</v>
       </c>
       <c r="KT2" t="n">
-        <v>403612</v>
+        <v>495066</v>
       </c>
       <c r="KU2" t="n">
-        <v>388984</v>
+        <v>115409</v>
       </c>
       <c r="KV2" t="n">
-        <v>481711</v>
+        <v>554203</v>
       </c>
       <c r="KW2" t="n">
-        <v>446521</v>
+        <v>1009519</v>
       </c>
       <c r="KX2" t="n">
-        <v>362002</v>
+        <v>790109</v>
       </c>
       <c r="KY2" t="n">
-        <v>827756</v>
+        <v>1181703</v>
       </c>
       <c r="KZ2" t="n">
-        <v>1066697</v>
+        <v>190977</v>
       </c>
       <c r="LA2" t="n">
-        <v>302704</v>
+        <v>166950</v>
       </c>
       <c r="LB2" t="n">
-        <v>1006382</v>
+        <v>239277</v>
       </c>
       <c r="LC2" t="n">
-        <v>1014390</v>
+        <v>355489</v>
       </c>
       <c r="LD2" t="n">
-        <v>153403</v>
+        <v>970095</v>
       </c>
       <c r="LE2" t="n">
-        <v>88778</v>
+        <v>661629</v>
       </c>
       <c r="LF2" t="n">
-        <v>33961</v>
+        <v>218269</v>
       </c>
       <c r="LG2" t="n">
-        <v>166041</v>
+        <v>868315</v>
       </c>
       <c r="LH2" t="n">
-        <v>1117762</v>
+        <v>604093</v>
       </c>
       <c r="LI2" t="n">
-        <v>580315</v>
+        <v>677539</v>
       </c>
       <c r="LJ2" t="n">
-        <v>484226</v>
+        <v>1092154</v>
       </c>
       <c r="LK2" t="n">
-        <v>203705</v>
+        <v>529156</v>
       </c>
       <c r="LL2" t="n">
-        <v>595733</v>
+        <v>1038619</v>
       </c>
       <c r="LM2" t="n">
-        <v>582914</v>
+        <v>259681</v>
       </c>
       <c r="LN2" t="n">
-        <v>1214460</v>
+        <v>79897</v>
       </c>
       <c r="LO2" t="n">
-        <v>675422</v>
+        <v>158025</v>
       </c>
       <c r="LP2" t="n">
-        <v>1013310</v>
+        <v>319221</v>
       </c>
       <c r="LQ2" t="n">
-        <v>909529</v>
+        <v>716988</v>
       </c>
       <c r="LR2" t="n">
-        <v>345436</v>
+        <v>409382</v>
       </c>
       <c r="LS2" t="n">
-        <v>948898</v>
+        <v>144258</v>
       </c>
       <c r="LT2" t="n">
-        <v>30165</v>
+        <v>825051</v>
       </c>
       <c r="LU2" t="n">
-        <v>706793</v>
+        <v>1189452</v>
       </c>
       <c r="LV2" t="n">
-        <v>1045553</v>
+        <v>1233745</v>
       </c>
       <c r="LW2" t="n">
-        <v>394788</v>
+        <v>962926</v>
       </c>
       <c r="LX2" t="n">
-        <v>1158992</v>
+        <v>892943</v>
       </c>
       <c r="LY2" t="n">
-        <v>101653</v>
+        <v>9075</v>
       </c>
       <c r="LZ2" t="n">
-        <v>511517</v>
+        <v>575172</v>
       </c>
       <c r="MA2" t="n">
-        <v>1020477</v>
+        <v>542246</v>
       </c>
       <c r="MB2" t="n">
-        <v>246744</v>
+        <v>698386</v>
       </c>
       <c r="MC2" t="n">
-        <v>997986</v>
+        <v>903220</v>
       </c>
       <c r="MD2" t="n">
-        <v>441471</v>
+        <v>1074952</v>
       </c>
       <c r="ME2" t="n">
-        <v>186807</v>
+        <v>175393</v>
       </c>
       <c r="MF2" t="n">
-        <v>289464</v>
+        <v>958316</v>
       </c>
       <c r="MG2" t="n">
-        <v>404005</v>
+        <v>488220</v>
       </c>
       <c r="MH2" t="n">
-        <v>866626</v>
+        <v>1135602</v>
       </c>
       <c r="MI2" t="n">
-        <v>749709</v>
+        <v>285105</v>
       </c>
       <c r="MJ2" t="n">
-        <v>912617</v>
+        <v>401142</v>
       </c>
       <c r="MK2" t="n">
-        <v>873287</v>
+        <v>902662</v>
       </c>
       <c r="ML2" t="n">
-        <v>138361</v>
+        <v>1056024</v>
       </c>
       <c r="MM2" t="n">
-        <v>178144</v>
+        <v>429293</v>
       </c>
       <c r="MN2" t="n">
-        <v>1008675</v>
+        <v>353307</v>
       </c>
       <c r="MO2" t="n">
-        <v>154466</v>
+        <v>1118819</v>
       </c>
       <c r="MP2" t="n">
-        <v>354531</v>
+        <v>462117</v>
       </c>
       <c r="MQ2" t="n">
-        <v>1065281</v>
+        <v>338693</v>
       </c>
       <c r="MR2" t="n">
-        <v>535075</v>
+        <v>448923</v>
       </c>
       <c r="MS2" t="n">
-        <v>787001</v>
+        <v>892993</v>
       </c>
       <c r="MT2" t="n">
-        <v>716613</v>
+        <v>194921</v>
       </c>
       <c r="MU2" t="n">
-        <v>933265</v>
+        <v>484351</v>
       </c>
       <c r="MV2" t="n">
-        <v>973127</v>
+        <v>243584</v>
       </c>
       <c r="MW2" t="n">
-        <v>868230</v>
+        <v>1074019</v>
       </c>
       <c r="MX2" t="n">
-        <v>95382</v>
+        <v>220600</v>
       </c>
       <c r="MY2" t="n">
-        <v>17778</v>
+        <v>145758</v>
       </c>
       <c r="MZ2" t="n">
-        <v>103321</v>
+        <v>1092019</v>
       </c>
       <c r="NA2" t="n">
-        <v>32065</v>
+        <v>234352</v>
       </c>
       <c r="NB2" t="n">
-        <v>286326</v>
+        <v>910054</v>
       </c>
       <c r="NC2" t="n">
-        <v>992609</v>
+        <v>16279</v>
       </c>
       <c r="ND2" t="n">
-        <v>903346</v>
+        <v>839948</v>
       </c>
       <c r="NE2" t="n">
-        <v>960581</v>
+        <v>202789</v>
       </c>
       <c r="NF2" t="n">
-        <v>487820</v>
+        <v>311873</v>
       </c>
       <c r="NG2" t="n">
-        <v>423996</v>
+        <v>252171</v>
       </c>
       <c r="NH2" t="n">
-        <v>225651</v>
+        <v>247406</v>
       </c>
       <c r="NI2" t="n">
-        <v>1120866</v>
+        <v>951383</v>
       </c>
       <c r="NJ2" t="n">
-        <v>381572</v>
+        <v>955442</v>
       </c>
       <c r="NK2" t="n">
-        <v>87022</v>
+        <v>710134</v>
       </c>
       <c r="NL2" t="n">
-        <v>834910</v>
+        <v>629838</v>
       </c>
       <c r="NM2" t="n">
-        <v>25387</v>
+        <v>334370</v>
       </c>
       <c r="NN2" t="n">
-        <v>58258</v>
+        <v>936459</v>
       </c>
       <c r="NO2" t="n">
-        <v>273961</v>
+        <v>389651</v>
       </c>
       <c r="NP2" t="n">
-        <v>977677</v>
+        <v>991763</v>
       </c>
       <c r="NQ2" t="n">
-        <v>1163317</v>
+        <v>164326</v>
       </c>
       <c r="NR2" t="n">
-        <v>191011</v>
+        <v>557946</v>
       </c>
       <c r="NS2" t="n">
-        <v>676604</v>
+        <v>368794</v>
       </c>
       <c r="NT2" t="n">
-        <v>69948</v>
+        <v>883483</v>
       </c>
       <c r="NU2" t="n">
-        <v>1200643</v>
+        <v>695822</v>
       </c>
       <c r="NV2" t="n">
-        <v>680974</v>
+        <v>277618</v>
       </c>
       <c r="NW2" t="n">
-        <v>337696</v>
+        <v>384963</v>
       </c>
       <c r="NX2" t="n">
-        <v>16752</v>
+        <v>214663</v>
       </c>
       <c r="NY2" t="n">
-        <v>36492</v>
+        <v>1237116</v>
       </c>
       <c r="NZ2" t="n">
-        <v>374268</v>
+        <v>835847</v>
       </c>
       <c r="OA2" t="n">
-        <v>10907</v>
+        <v>355427</v>
       </c>
       <c r="OB2" t="n">
-        <v>815152</v>
+        <v>291026</v>
       </c>
       <c r="OC2" t="n">
-        <v>1132740</v>
+        <v>441103</v>
       </c>
       <c r="OD2" t="n">
-        <v>1072871</v>
+        <v>508110</v>
       </c>
       <c r="OE2" t="n">
-        <v>720443</v>
+        <v>1178428</v>
       </c>
       <c r="OF2" t="n">
-        <v>649882</v>
+        <v>120569</v>
       </c>
       <c r="OG2" t="n">
-        <v>486721</v>
+        <v>364269</v>
       </c>
       <c r="OH2" t="n">
-        <v>141621</v>
+        <v>378282</v>
       </c>
       <c r="OI2" t="n">
-        <v>863890</v>
+        <v>973064</v>
       </c>
       <c r="OJ2" t="n">
-        <v>461719</v>
+        <v>197035</v>
       </c>
       <c r="OK2" t="n">
-        <v>1147392</v>
+        <v>30072</v>
       </c>
       <c r="OL2" t="n">
-        <v>1202442</v>
+        <v>493298</v>
       </c>
       <c r="OM2" t="n">
-        <v>845874</v>
+        <v>1163890</v>
       </c>
       <c r="ON2" t="n">
-        <v>625768</v>
+        <v>85111</v>
       </c>
       <c r="OO2" t="n">
-        <v>1047871</v>
+        <v>103300</v>
       </c>
       <c r="OP2" t="n">
-        <v>1022514</v>
+        <v>1140719</v>
       </c>
       <c r="OQ2" t="n">
-        <v>275721</v>
+        <v>5582</v>
       </c>
       <c r="OR2" t="n">
-        <v>122165</v>
+        <v>1157450</v>
       </c>
       <c r="OS2" t="n">
-        <v>273033</v>
+        <v>444470</v>
       </c>
       <c r="OT2" t="n">
-        <v>930456</v>
+        <v>480133</v>
       </c>
       <c r="OU2" t="n">
-        <v>695186</v>
+        <v>655022</v>
       </c>
       <c r="OV2" t="n">
-        <v>359137</v>
+        <v>1086995</v>
       </c>
       <c r="OW2" t="n">
-        <v>1167195</v>
+        <v>268265</v>
       </c>
       <c r="OX2" t="n">
-        <v>690603</v>
+        <v>1016242</v>
       </c>
       <c r="OY2" t="n">
-        <v>254630</v>
+        <v>581068</v>
       </c>
       <c r="OZ2" t="n">
-        <v>683651</v>
+        <v>1077300</v>
       </c>
       <c r="PA2" t="n">
-        <v>64066</v>
+        <v>1198872</v>
       </c>
       <c r="PB2" t="n">
-        <v>899001</v>
+        <v>1064377</v>
       </c>
       <c r="PC2" t="n">
-        <v>921520</v>
+        <v>816607</v>
       </c>
       <c r="PD2" t="n">
-        <v>468709</v>
+        <v>230543</v>
       </c>
       <c r="PE2" t="n">
-        <v>436286</v>
+        <v>669085</v>
       </c>
       <c r="PF2" t="n">
-        <v>609792</v>
+        <v>783159</v>
       </c>
       <c r="PG2" t="n">
-        <v>542608</v>
+        <v>272686</v>
       </c>
       <c r="PH2" t="n">
-        <v>840613</v>
+        <v>804042</v>
       </c>
       <c r="PI2" t="n">
-        <v>554969</v>
+        <v>877073</v>
       </c>
       <c r="PJ2" t="n">
-        <v>566248</v>
+        <v>392118</v>
       </c>
       <c r="PK2" t="n">
-        <v>260274</v>
+        <v>489552</v>
       </c>
       <c r="PL2" t="n">
-        <v>1025716</v>
+        <v>295337</v>
       </c>
       <c r="PM2" t="n">
-        <v>81711</v>
+        <v>1095991</v>
       </c>
       <c r="PN2" t="n">
-        <v>0</v>
+        <v>538852</v>
       </c>
       <c r="PO2" t="n">
-        <v>744380</v>
+        <v>947741</v>
       </c>
       <c r="PP2" t="n">
-        <v>756658</v>
+        <v>546603</v>
       </c>
       <c r="PQ2" t="n">
-        <v>180036</v>
+        <v>935131</v>
       </c>
       <c r="PR2" t="n">
-        <v>477853</v>
+        <v>812563</v>
       </c>
       <c r="PS2" t="n">
-        <v>539246</v>
+        <v>1083860</v>
       </c>
       <c r="PT2" t="n">
-        <v>392176</v>
+        <v>450119</v>
       </c>
       <c r="PU2" t="n">
-        <v>139943</v>
+        <v>406491</v>
       </c>
       <c r="PV2" t="n">
-        <v>149502</v>
+        <v>735370</v>
       </c>
       <c r="PW2" t="n">
-        <v>867</v>
+        <v>624625</v>
       </c>
       <c r="PX2" t="n">
-        <v>20298</v>
+        <v>104455</v>
       </c>
       <c r="PY2" t="n">
-        <v>354242</v>
+        <v>1139126</v>
       </c>
       <c r="PZ2" t="n">
-        <v>679506</v>
+        <v>380206</v>
       </c>
       <c r="QA2" t="n">
-        <v>176048</v>
+        <v>462408</v>
       </c>
       <c r="QB2" t="n">
-        <v>615358</v>
+        <v>562891</v>
       </c>
       <c r="QC2" t="n">
-        <v>883396</v>
+        <v>725889</v>
       </c>
       <c r="QD2" t="n">
-        <v>702929</v>
+        <v>91246</v>
       </c>
       <c r="QE2" t="n">
-        <v>1170658</v>
+        <v>738672</v>
       </c>
       <c r="QF2" t="n">
-        <v>667189</v>
+        <v>117632</v>
       </c>
       <c r="QG2" t="n">
-        <v>651238</v>
+        <v>398874</v>
       </c>
       <c r="QH2" t="n">
-        <v>184628</v>
+        <v>1027676</v>
       </c>
       <c r="QI2" t="n">
-        <v>1040068</v>
+        <v>733866</v>
       </c>
       <c r="QJ2" t="n">
-        <v>640069</v>
+        <v>510791</v>
       </c>
       <c r="QK2" t="n">
-        <v>780024</v>
+        <v>68101</v>
       </c>
       <c r="QL2" t="n">
-        <v>581124</v>
+        <v>966334</v>
       </c>
       <c r="QM2" t="n">
-        <v>781666</v>
+        <v>720607</v>
       </c>
       <c r="QN2" t="n">
-        <v>29067</v>
+        <v>908620</v>
       </c>
       <c r="QO2" t="n">
-        <v>131312</v>
+        <v>81623</v>
       </c>
       <c r="QP2" t="n">
-        <v>319743</v>
+        <v>711267</v>
       </c>
       <c r="QQ2" t="n">
-        <v>829206</v>
+        <v>1071296</v>
       </c>
       <c r="QR2" t="n">
-        <v>373060</v>
+        <v>616001</v>
       </c>
       <c r="QS2" t="n">
-        <v>794539</v>
+        <v>173724</v>
       </c>
       <c r="QT2" t="n">
-        <v>194866</v>
+        <v>905879</v>
       </c>
       <c r="QU2" t="n">
-        <v>11901</v>
+        <v>928706</v>
       </c>
       <c r="QV2" t="n">
-        <v>293379</v>
+        <v>32789</v>
       </c>
       <c r="QW2" t="n">
-        <v>239057</v>
+        <v>224294</v>
       </c>
       <c r="QX2" t="n">
-        <v>386421</v>
+        <v>1067546</v>
       </c>
       <c r="QY2" t="n">
-        <v>634962</v>
+        <v>70053</v>
       </c>
       <c r="QZ2" t="n">
-        <v>505155</v>
+        <v>856620</v>
       </c>
       <c r="RA2" t="n">
-        <v>945681</v>
+        <v>581447</v>
       </c>
       <c r="RB2" t="n">
-        <v>100496</v>
+        <v>1062136</v>
       </c>
       <c r="RC2" t="n">
-        <v>16461</v>
+        <v>621020</v>
       </c>
       <c r="RD2" t="n">
-        <v>106402</v>
+        <v>726770</v>
       </c>
       <c r="RE2" t="n">
-        <v>22056</v>
+        <v>128707</v>
       </c>
       <c r="RF2" t="n">
-        <v>308229</v>
+        <v>313607</v>
       </c>
       <c r="RG2" t="n">
-        <v>348658</v>
+        <v>225443</v>
       </c>
       <c r="RH2" t="n">
-        <v>1090372</v>
+        <v>690938</v>
       </c>
       <c r="RI2" t="n">
-        <v>770098</v>
+        <v>17974</v>
       </c>
       <c r="RJ2" t="n">
-        <v>1164762</v>
+        <v>262791</v>
       </c>
       <c r="RK2" t="n">
-        <v>332120</v>
+        <v>644713</v>
       </c>
       <c r="RL2" t="n">
-        <v>201883</v>
+        <v>530751</v>
       </c>
       <c r="RM2" t="n">
-        <v>470942</v>
+        <v>466791</v>
       </c>
       <c r="RN2" t="n">
-        <v>521544</v>
+        <v>380083</v>
       </c>
       <c r="RO2" t="n">
-        <v>51345</v>
+        <v>240880</v>
       </c>
       <c r="RP2" t="n">
-        <v>223458</v>
+        <v>849196</v>
       </c>
       <c r="RQ2" t="n">
-        <v>45383</v>
+        <v>182605</v>
       </c>
       <c r="RR2" t="n">
-        <v>1003149</v>
+        <v>1002415</v>
       </c>
       <c r="RS2" t="n">
-        <v>385702</v>
+        <v>1166611</v>
       </c>
       <c r="RT2" t="n">
-        <v>13948</v>
+        <v>471988</v>
       </c>
       <c r="RU2" t="n">
-        <v>855681</v>
+        <v>93033</v>
       </c>
       <c r="RV2" t="n">
-        <v>946989</v>
+        <v>403658</v>
       </c>
       <c r="RW2" t="n">
-        <v>771185</v>
+        <v>582866</v>
       </c>
       <c r="RX2" t="n">
-        <v>431394</v>
+        <v>681630</v>
       </c>
       <c r="RY2" t="n">
-        <v>500329</v>
+        <v>1212991</v>
       </c>
       <c r="RZ2" t="n">
-        <v>166850</v>
+        <v>1227116</v>
       </c>
       <c r="SA2" t="n">
-        <v>963717</v>
+        <v>1195855</v>
       </c>
       <c r="SB2" t="n">
-        <v>312463</v>
+        <v>450813</v>
       </c>
       <c r="SC2" t="n">
-        <v>1079531</v>
+        <v>412993</v>
       </c>
       <c r="SD2" t="n">
-        <v>656014</v>
+        <v>420896</v>
       </c>
       <c r="SE2" t="n">
-        <v>1011962</v>
+        <v>12889</v>
       </c>
       <c r="SF2" t="n">
-        <v>197153</v>
+        <v>184528</v>
       </c>
       <c r="SG2" t="n">
-        <v>337594</v>
+        <v>670890</v>
       </c>
       <c r="SH2" t="n">
-        <v>586476</v>
+        <v>345001</v>
       </c>
       <c r="SI2" t="n">
-        <v>591430</v>
+        <v>142163</v>
       </c>
       <c r="SJ2" t="n">
-        <v>1109766</v>
+        <v>329070</v>
       </c>
       <c r="SK2" t="n">
-        <v>1037859</v>
+        <v>1219061</v>
       </c>
       <c r="SL2" t="n">
-        <v>1135743</v>
+        <v>97004</v>
       </c>
       <c r="SM2" t="n">
-        <v>1020261</v>
+        <v>873136</v>
       </c>
       <c r="SN2" t="n">
-        <v>898204</v>
+        <v>843284</v>
       </c>
       <c r="SO2" t="n">
-        <v>1108059</v>
+        <v>264230</v>
       </c>
       <c r="SP2" t="n">
-        <v>397349</v>
+        <v>65072</v>
       </c>
       <c r="SQ2" t="n">
-        <v>645962</v>
+        <v>693380</v>
       </c>
       <c r="SR2" t="n">
-        <v>10586</v>
+        <v>257883</v>
       </c>
       <c r="SS2" t="n">
-        <v>114660</v>
+        <v>162998</v>
       </c>
       <c r="ST2" t="n">
-        <v>371981</v>
+        <v>614644</v>
       </c>
       <c r="SU2" t="n">
-        <v>838613</v>
+        <v>153069</v>
       </c>
       <c r="SV2" t="n">
-        <v>159390</v>
+        <v>608194</v>
       </c>
       <c r="SW2" t="n">
-        <v>845786</v>
+        <v>730403</v>
       </c>
       <c r="SX2" t="n">
-        <v>434800</v>
+        <v>801920</v>
       </c>
       <c r="SY2" t="n">
-        <v>531188</v>
+        <v>1143822</v>
       </c>
       <c r="SZ2" t="n">
-        <v>663037</v>
+        <v>800170</v>
       </c>
       <c r="TA2" t="n">
-        <v>526979</v>
+        <v>58981</v>
       </c>
       <c r="TB2" t="n">
-        <v>139907</v>
+        <v>376568</v>
       </c>
       <c r="TC2" t="n">
-        <v>4831</v>
+        <v>189387</v>
       </c>
       <c r="TD2" t="n">
-        <v>811198</v>
+        <v>150451</v>
       </c>
       <c r="TE2" t="n">
-        <v>777373</v>
+        <v>45061</v>
       </c>
       <c r="TF2" t="n">
-        <v>641955</v>
+        <v>289556</v>
       </c>
       <c r="TG2" t="n">
-        <v>752719</v>
+        <v>245925</v>
       </c>
       <c r="TH2" t="n">
-        <v>299697</v>
+        <v>467539</v>
       </c>
       <c r="TI2" t="n">
-        <v>980985</v>
+        <v>944180</v>
       </c>
       <c r="TJ2" t="n">
-        <v>584554</v>
+        <v>134459</v>
       </c>
       <c r="TK2" t="n">
-        <v>37725</v>
+        <v>213046</v>
       </c>
       <c r="TL2" t="n">
-        <v>15207</v>
+        <v>224530</v>
       </c>
       <c r="TM2" t="n">
-        <v>1119343</v>
+        <v>596315</v>
       </c>
       <c r="TN2" t="n">
-        <v>901716</v>
+        <v>477934</v>
       </c>
       <c r="TO2" t="n">
-        <v>1030547</v>
+        <v>9080</v>
       </c>
       <c r="TP2" t="n">
-        <v>861938</v>
+        <v>366235</v>
       </c>
       <c r="TQ2" t="n">
-        <v>846040</v>
+        <v>368764</v>
       </c>
       <c r="TR2" t="n">
-        <v>12367</v>
+        <v>194</v>
       </c>
       <c r="TS2" t="n">
-        <v>537553</v>
+        <v>303500</v>
       </c>
       <c r="TT2" t="n">
-        <v>1054682</v>
+        <v>49047</v>
       </c>
       <c r="TU2" t="n">
-        <v>719498</v>
+        <v>839332</v>
       </c>
       <c r="TV2" t="n">
-        <v>1042525</v>
+        <v>1131134</v>
       </c>
       <c r="TW2" t="n">
-        <v>370290</v>
+        <v>1017243</v>
       </c>
       <c r="TX2" t="n">
-        <v>411108</v>
+        <v>487725</v>
       </c>
       <c r="TY2" t="n">
-        <v>346370</v>
+        <v>531093</v>
       </c>
       <c r="TZ2" t="n">
-        <v>1092930</v>
+        <v>225254</v>
       </c>
       <c r="UA2" t="n">
-        <v>307961</v>
+        <v>678622</v>
       </c>
       <c r="UB2" t="n">
-        <v>144434</v>
+        <v>1118900</v>
       </c>
       <c r="UC2" t="n">
-        <v>567809</v>
+        <v>809717</v>
       </c>
       <c r="UD2" t="n">
-        <v>498834</v>
+        <v>479689</v>
       </c>
       <c r="UE2" t="n">
-        <v>669647</v>
+        <v>89684</v>
       </c>
       <c r="UF2" t="n">
-        <v>77421</v>
+        <v>436148</v>
       </c>
       <c r="UG2" t="n">
-        <v>214955</v>
+        <v>509431</v>
       </c>
       <c r="UH2" t="n">
-        <v>1176654</v>
+        <v>871370</v>
       </c>
       <c r="UI2" t="n">
-        <v>765522</v>
+        <v>590216</v>
       </c>
       <c r="UJ2" t="n">
-        <v>1076398</v>
+        <v>31812</v>
       </c>
       <c r="UK2" t="n">
-        <v>263414</v>
+        <v>61937</v>
       </c>
       <c r="UL2" t="n">
-        <v>68586</v>
+        <v>324770</v>
       </c>
       <c r="UM2" t="n">
-        <v>734700</v>
+        <v>1174576</v>
       </c>
       <c r="UN2" t="n">
-        <v>54970</v>
+        <v>37385</v>
       </c>
       <c r="UO2" t="n">
-        <v>1114234</v>
+        <v>145393</v>
       </c>
       <c r="UP2" t="n">
-        <v>123731</v>
+        <v>643126</v>
       </c>
       <c r="UQ2" t="n">
-        <v>688902</v>
+        <v>1014541</v>
       </c>
       <c r="UR2" t="n">
-        <v>993696</v>
+        <v>821277</v>
       </c>
       <c r="US2" t="n">
-        <v>368549</v>
+        <v>576718</v>
       </c>
       <c r="UT2" t="n">
-        <v>850735</v>
+        <v>112840</v>
       </c>
       <c r="UU2" t="n">
-        <v>220910</v>
+        <v>191827</v>
       </c>
       <c r="UV2" t="n">
-        <v>735292</v>
+        <v>744762</v>
       </c>
       <c r="UW2" t="n">
-        <v>1137615</v>
+        <v>699632</v>
       </c>
       <c r="UX2" t="n">
-        <v>113072</v>
+        <v>969003</v>
       </c>
       <c r="UY2" t="n">
-        <v>958621</v>
+        <v>432407</v>
       </c>
       <c r="UZ2" t="n">
-        <v>806607</v>
+        <v>333301</v>
       </c>
       <c r="VA2" t="n">
-        <v>588054</v>
+        <v>1175392</v>
       </c>
       <c r="VB2" t="n">
-        <v>604817</v>
+        <v>1166195</v>
       </c>
       <c r="VC2" t="n">
-        <v>689686</v>
+        <v>1040480</v>
       </c>
       <c r="VD2" t="n">
-        <v>401257</v>
+        <v>764554</v>
       </c>
       <c r="VE2" t="n">
-        <v>617878</v>
+        <v>853814</v>
       </c>
       <c r="VF2" t="n">
-        <v>515065</v>
+        <v>1162423</v>
       </c>
       <c r="VG2" t="n">
-        <v>406097</v>
+        <v>485421</v>
       </c>
       <c r="VH2" t="n">
-        <v>1005352</v>
+        <v>1026500</v>
       </c>
       <c r="VI2" t="n">
-        <v>839766</v>
+        <v>1025360</v>
       </c>
       <c r="VJ2" t="n">
-        <v>524803</v>
+        <v>829152</v>
       </c>
       <c r="VK2" t="n">
-        <v>538509</v>
+        <v>109744</v>
       </c>
       <c r="VL2" t="n">
-        <v>923746</v>
+        <v>617356</v>
       </c>
       <c r="VM2" t="n">
-        <v>1112873</v>
+        <v>846789</v>
       </c>
       <c r="VN2" t="n">
-        <v>109210</v>
+        <v>1205867</v>
       </c>
       <c r="VO2" t="n">
-        <v>978625</v>
+        <v>651602</v>
       </c>
       <c r="VP2" t="n">
-        <v>304622</v>
+        <v>996462</v>
       </c>
       <c r="VQ2" t="n">
-        <v>548309</v>
+        <v>194334</v>
       </c>
       <c r="VR2" t="n">
-        <v>572435</v>
+        <v>1083832</v>
       </c>
       <c r="VS2" t="n">
-        <v>788325</v>
+        <v>747014</v>
       </c>
       <c r="VT2" t="n">
-        <v>581745</v>
+        <v>1080213</v>
       </c>
       <c r="VU2" t="n">
-        <v>83460</v>
+        <v>698297</v>
       </c>
       <c r="VV2" t="n">
-        <v>878465</v>
+        <v>364527</v>
       </c>
       <c r="VW2" t="n">
-        <v>722546</v>
+        <v>617642</v>
       </c>
       <c r="VX2" t="n">
-        <v>292260</v>
+        <v>1110724</v>
       </c>
       <c r="VY2" t="n">
-        <v>177940</v>
+        <v>375153</v>
       </c>
       <c r="VZ2" t="n">
-        <v>422325</v>
+        <v>139369</v>
       </c>
       <c r="WA2" t="n">
-        <v>693473</v>
+        <v>712192</v>
       </c>
       <c r="WB2" t="n">
-        <v>758641</v>
+        <v>281709</v>
       </c>
       <c r="WC2" t="n">
-        <v>314760</v>
+        <v>627918</v>
       </c>
       <c r="WD2" t="n">
-        <v>887453</v>
+        <v>521229</v>
       </c>
       <c r="WE2" t="n">
-        <v>239481</v>
+        <v>308931</v>
       </c>
       <c r="WF2" t="n">
-        <v>519733</v>
+        <v>665058</v>
       </c>
       <c r="WG2" t="n">
-        <v>630544</v>
+        <v>21318</v>
       </c>
       <c r="WH2" t="n">
-        <v>155477</v>
+        <v>886667</v>
       </c>
       <c r="WI2" t="n">
-        <v>91710</v>
+        <v>169305</v>
       </c>
       <c r="WJ2" t="n">
-        <v>222111</v>
+        <v>41463</v>
       </c>
       <c r="WK2" t="n">
-        <v>565629</v>
+        <v>1021814</v>
       </c>
       <c r="WL2" t="n">
-        <v>229564</v>
+        <v>491932</v>
       </c>
       <c r="WM2" t="n">
-        <v>293057</v>
+        <v>793941</v>
       </c>
       <c r="WN2" t="n">
-        <v>732420</v>
+        <v>159395</v>
       </c>
       <c r="WO2" t="n">
-        <v>562288</v>
+        <v>1181723</v>
       </c>
       <c r="WP2" t="n">
-        <v>571237</v>
+        <v>126713</v>
       </c>
       <c r="WQ2" t="n">
-        <v>91847</v>
+        <v>1079049</v>
       </c>
       <c r="WR2" t="n">
-        <v>1183620</v>
+        <v>1210059</v>
       </c>
       <c r="WS2" t="n">
-        <v>196090</v>
+        <v>954316</v>
       </c>
       <c r="WT2" t="n">
-        <v>521136</v>
+        <v>1896</v>
       </c>
       <c r="WU2" t="n">
-        <v>301516</v>
+        <v>619318</v>
       </c>
       <c r="WV2" t="n">
-        <v>512508</v>
+        <v>714751</v>
       </c>
       <c r="WW2" t="n">
-        <v>832544</v>
+        <v>252655</v>
       </c>
       <c r="WX2" t="n">
-        <v>898095</v>
+        <v>373211</v>
       </c>
       <c r="WY2" t="n">
-        <v>99095</v>
+        <v>311358</v>
       </c>
       <c r="WZ2" t="n">
-        <v>256729</v>
+        <v>640824</v>
       </c>
       <c r="XA2" t="n">
-        <v>820655</v>
+        <v>865223</v>
       </c>
       <c r="XB2" t="n">
-        <v>509015</v>
+        <v>137714</v>
       </c>
       <c r="XC2" t="n">
-        <v>740954</v>
+        <v>657082</v>
       </c>
       <c r="XD2" t="n">
-        <v>704691</v>
+        <v>644557</v>
       </c>
       <c r="XE2" t="n">
-        <v>940384</v>
+        <v>469467</v>
       </c>
       <c r="XF2" t="n">
-        <v>481508</v>
+        <v>560687</v>
       </c>
       <c r="XG2" t="n">
-        <v>551434</v>
+        <v>734126</v>
       </c>
       <c r="XH2" t="n">
-        <v>269680</v>
+        <v>504044</v>
       </c>
       <c r="XI2" t="n">
-        <v>12405</v>
+        <v>106782</v>
       </c>
       <c r="XJ2" t="n">
-        <v>614248</v>
+        <v>641721</v>
       </c>
       <c r="XK2" t="n">
-        <v>924661</v>
+        <v>452394</v>
       </c>
       <c r="XL2" t="n">
-        <v>228590</v>
+        <v>92008</v>
       </c>
       <c r="XM2" t="n">
-        <v>574600</v>
+        <v>179107</v>
       </c>
       <c r="XN2" t="n">
-        <v>1156771</v>
+        <v>993201</v>
       </c>
       <c r="XO2" t="n">
-        <v>297765</v>
+        <v>468389</v>
       </c>
       <c r="XP2" t="n">
-        <v>79296</v>
+        <v>99833</v>
       </c>
       <c r="XQ2" t="n">
-        <v>968466</v>
+        <v>588466</v>
       </c>
       <c r="XR2" t="n">
-        <v>428377</v>
+        <v>45030</v>
       </c>
       <c r="XS2" t="n">
-        <v>197465</v>
+        <v>976380</v>
       </c>
       <c r="XT2" t="n">
-        <v>528881</v>
+        <v>1069295</v>
       </c>
       <c r="XU2" t="n">
-        <v>514081</v>
+        <v>552262</v>
       </c>
       <c r="XV2" t="n">
-        <v>800297</v>
+        <v>541363</v>
       </c>
       <c r="XW2" t="n">
-        <v>661413</v>
+        <v>675018</v>
       </c>
       <c r="XX2" t="n">
-        <v>845103</v>
+        <v>861871</v>
       </c>
       <c r="XY2" t="n">
-        <v>577311</v>
+        <v>908250</v>
       </c>
       <c r="XZ2" t="n">
-        <v>1070534</v>
+        <v>46007</v>
       </c>
       <c r="YA2" t="n">
-        <v>440303</v>
+        <v>30775</v>
       </c>
       <c r="YB2" t="n">
-        <v>1125976</v>
+        <v>221949</v>
       </c>
       <c r="YC2" t="n">
-        <v>340780</v>
+        <v>784994</v>
       </c>
       <c r="YD2" t="n">
-        <v>1218271</v>
+        <v>299875</v>
       </c>
       <c r="YE2" t="n">
-        <v>21298</v>
+        <v>2620</v>
       </c>
       <c r="YF2" t="n">
-        <v>909842</v>
+        <v>1221032</v>
       </c>
       <c r="YG2" t="n">
-        <v>340110</v>
+        <v>245629</v>
       </c>
       <c r="YH2" t="n">
-        <v>491985</v>
+        <v>160600</v>
       </c>
       <c r="YI2" t="n">
-        <v>78588</v>
+        <v>281170</v>
       </c>
       <c r="YJ2" t="n">
-        <v>886526</v>
+        <v>116253</v>
       </c>
       <c r="YK2" t="n">
-        <v>290182</v>
+        <v>296170</v>
       </c>
       <c r="YL2" t="n">
-        <v>1123369</v>
+        <v>648975</v>
       </c>
       <c r="YM2" t="n">
-        <v>934980</v>
+        <v>325427</v>
       </c>
       <c r="YN2" t="n">
-        <v>106708</v>
+        <v>410043</v>
       </c>
       <c r="YO2" t="n">
-        <v>1197002</v>
+        <v>316313</v>
       </c>
       <c r="YP2" t="n">
-        <v>325319</v>
+        <v>111097</v>
       </c>
       <c r="YQ2" t="n">
-        <v>114741</v>
+        <v>475893</v>
       </c>
       <c r="YR2" t="n">
-        <v>855820</v>
+        <v>48940</v>
       </c>
       <c r="YS2" t="n">
-        <v>1143779</v>
+        <v>994554</v>
       </c>
       <c r="YT2" t="n">
-        <v>1055130</v>
+        <v>1191071</v>
       </c>
       <c r="YU2" t="n">
-        <v>418349</v>
+        <v>416263</v>
       </c>
       <c r="YV2" t="n">
-        <v>590709</v>
+        <v>518531</v>
       </c>
       <c r="YW2" t="n">
-        <v>1149913</v>
+        <v>1036536</v>
       </c>
       <c r="YX2" t="n">
-        <v>1091984</v>
+        <v>968297</v>
       </c>
       <c r="YY2" t="n">
-        <v>411993</v>
+        <v>553335</v>
       </c>
       <c r="YZ2" t="n">
-        <v>476267</v>
+        <v>864023</v>
       </c>
       <c r="ZA2" t="n">
-        <v>110406</v>
+        <v>794559</v>
       </c>
       <c r="ZB2" t="n">
-        <v>66738</v>
+        <v>797745</v>
       </c>
       <c r="ZC2" t="n">
-        <v>601203</v>
+        <v>766179</v>
       </c>
       <c r="ZD2" t="n">
-        <v>556058</v>
+        <v>1013644</v>
       </c>
       <c r="ZE2" t="n">
-        <v>365820</v>
+        <v>99996</v>
       </c>
       <c r="ZF2" t="n">
-        <v>53291</v>
+        <v>506270</v>
       </c>
       <c r="ZG2" t="n">
-        <v>843606</v>
+        <v>1020937</v>
       </c>
       <c r="ZH2" t="n">
-        <v>125909</v>
+        <v>571155</v>
       </c>
       <c r="ZI2" t="n">
-        <v>586032</v>
+        <v>219222</v>
       </c>
       <c r="ZJ2" t="n">
-        <v>438896</v>
+        <v>825546</v>
       </c>
       <c r="ZK2" t="n">
-        <v>616013</v>
+        <v>527086</v>
       </c>
       <c r="ZL2" t="n">
-        <v>1097536</v>
+        <v>198794</v>
       </c>
       <c r="ZM2" t="n">
-        <v>64364</v>
+        <v>147853</v>
       </c>
       <c r="ZN2" t="n">
-        <v>208652</v>
+        <v>501136</v>
       </c>
       <c r="ZO2" t="n">
-        <v>543691</v>
+        <v>50455</v>
       </c>
       <c r="ZP2" t="n">
-        <v>1209355</v>
+        <v>583809</v>
       </c>
       <c r="ZQ2" t="n">
-        <v>551491</v>
+        <v>94824</v>
       </c>
       <c r="ZR2" t="n">
-        <v>1221030</v>
+        <v>566237</v>
       </c>
       <c r="ZS2" t="n">
-        <v>320034</v>
+        <v>1103143</v>
       </c>
       <c r="ZT2" t="n">
-        <v>493771</v>
+        <v>870061</v>
       </c>
       <c r="ZU2" t="n">
-        <v>996910</v>
+        <v>76413</v>
       </c>
       <c r="ZV2" t="n">
-        <v>487494</v>
+        <v>208521</v>
       </c>
       <c r="ZW2" t="n">
-        <v>398324</v>
+        <v>732763</v>
       </c>
       <c r="ZX2" t="n">
-        <v>393433</v>
+        <v>1106379</v>
       </c>
       <c r="ZY2" t="n">
-        <v>150848</v>
+        <v>326873</v>
       </c>
       <c r="ZZ2" t="n">
-        <v>345122</v>
+        <v>36504</v>
       </c>
       <c r="AAA2" t="n">
-        <v>928837</v>
+        <v>635499</v>
       </c>
       <c r="AAB2" t="n">
-        <v>554881</v>
+        <v>729785</v>
       </c>
       <c r="AAC2" t="n">
-        <v>942730</v>
+        <v>346647</v>
       </c>
       <c r="AAD2" t="n">
-        <v>1001452</v>
+        <v>405866</v>
       </c>
       <c r="AAE2" t="n">
-        <v>750918</v>
+        <v>540976</v>
       </c>
       <c r="AAF2" t="n">
-        <v>880659</v>
+        <v>1203235</v>
       </c>
       <c r="AAG2" t="n">
-        <v>626508</v>
+        <v>45463</v>
       </c>
       <c r="AAH2" t="n">
-        <v>433838</v>
+        <v>1173665</v>
       </c>
       <c r="AAI2" t="n">
-        <v>251040</v>
+        <v>918542</v>
       </c>
       <c r="AAJ2" t="n">
-        <v>1084978</v>
+        <v>84710</v>
       </c>
       <c r="AAK2" t="n">
-        <v>1056800</v>
+        <v>1125099</v>
       </c>
       <c r="AAL2" t="n">
-        <v>322002</v>
+        <v>701660</v>
       </c>
       <c r="AAM2" t="n">
-        <v>221108</v>
+        <v>22228</v>
       </c>
       <c r="AAN2" t="n">
-        <v>274443</v>
+        <v>445880</v>
       </c>
       <c r="AAO2" t="n">
-        <v>783910</v>
+        <v>74623</v>
       </c>
       <c r="AAP2" t="n">
-        <v>1127075</v>
+        <v>304851</v>
       </c>
       <c r="AAQ2" t="n">
-        <v>606670</v>
+        <v>359246</v>
       </c>
       <c r="AAR2" t="n">
-        <v>999188</v>
+        <v>534729</v>
       </c>
       <c r="AAS2" t="n">
-        <v>1190748</v>
+        <v>113743</v>
       </c>
       <c r="AAT2" t="n">
-        <v>168501</v>
+        <v>800835</v>
       </c>
       <c r="AAU2" t="n">
-        <v>738416</v>
+        <v>1123057</v>
       </c>
       <c r="AAV2" t="n">
-        <v>527942</v>
+        <v>12954</v>
       </c>
       <c r="AAW2" t="n">
-        <v>500979</v>
+        <v>694881</v>
       </c>
       <c r="AAX2" t="n">
-        <v>238691</v>
+        <v>231483</v>
       </c>
       <c r="AAY2" t="n">
-        <v>1053304</v>
+        <v>383914</v>
       </c>
       <c r="AAZ2" t="n">
-        <v>1208416</v>
+        <v>350433</v>
       </c>
       <c r="ABA2" t="n">
-        <v>6497</v>
+        <v>216751</v>
       </c>
       <c r="ABB2" t="n">
-        <v>504333</v>
+        <v>609387</v>
       </c>
       <c r="ABC2" t="n">
-        <v>824508</v>
+        <v>52927</v>
       </c>
       <c r="ABD2" t="n">
-        <v>1191850</v>
+        <v>386053</v>
       </c>
       <c r="ABE2" t="n">
-        <v>832525</v>
+        <v>559889</v>
       </c>
       <c r="ABF2" t="n">
-        <v>791609</v>
+        <v>1169739</v>
       </c>
       <c r="ABG2" t="n">
-        <v>702999</v>
+        <v>771046</v>
       </c>
       <c r="ABH2" t="n">
-        <v>861076</v>
+        <v>358522</v>
       </c>
       <c r="ABI2" t="n">
-        <v>459315</v>
+        <v>343562</v>
       </c>
       <c r="ABJ2" t="n">
-        <v>820293</v>
+        <v>601992</v>
       </c>
       <c r="ABK2" t="n">
-        <v>1152034</v>
+        <v>586385</v>
       </c>
       <c r="ABL2" t="n">
-        <v>768672</v>
+        <v>43269</v>
       </c>
       <c r="ABM2" t="n">
-        <v>597734</v>
+        <v>840777</v>
       </c>
       <c r="ABN2" t="n">
-        <v>732840</v>
+        <v>73495</v>
       </c>
       <c r="ABO2" t="n">
-        <v>69191</v>
+        <v>18611</v>
       </c>
       <c r="ABP2" t="n">
-        <v>605664</v>
+        <v>179670</v>
       </c>
       <c r="ABQ2" t="n">
-        <v>751957</v>
+        <v>265020</v>
       </c>
       <c r="ABR2" t="n">
-        <v>234968</v>
+        <v>516960</v>
       </c>
       <c r="ABS2" t="n">
-        <v>792389</v>
+        <v>208212</v>
       </c>
       <c r="ABT2" t="n">
-        <v>327603</v>
+        <v>781690</v>
       </c>
       <c r="ABU2" t="n">
-        <v>1131987</v>
+        <v>657893</v>
       </c>
       <c r="ABV2" t="n">
-        <v>847854</v>
+        <v>159464</v>
       </c>
       <c r="ABW2" t="n">
-        <v>188320</v>
+        <v>972791</v>
       </c>
       <c r="ABX2" t="n">
-        <v>456814</v>
+        <v>394409</v>
       </c>
       <c r="ABY2" t="n">
-        <v>237604</v>
+        <v>528453</v>
       </c>
       <c r="ABZ2" t="n">
-        <v>691627</v>
+        <v>486983</v>
       </c>
       <c r="ACA2" t="n">
-        <v>239477</v>
+        <v>942569</v>
       </c>
       <c r="ACB2" t="n">
-        <v>352812</v>
+        <v>806736</v>
       </c>
       <c r="ACC2" t="n">
-        <v>206178</v>
+        <v>981002</v>
       </c>
       <c r="ACD2" t="n">
-        <v>426460</v>
+        <v>417980</v>
       </c>
       <c r="ACE2" t="n">
-        <v>549918</v>
+        <v>1058865</v>
       </c>
       <c r="ACF2" t="n">
-        <v>95792</v>
+        <v>682623</v>
       </c>
       <c r="ACG2" t="n">
-        <v>452503</v>
+        <v>860886</v>
       </c>
       <c r="ACH2" t="n">
-        <v>1027206</v>
+        <v>316609</v>
       </c>
       <c r="ACI2" t="n">
-        <v>1202852</v>
+        <v>455339</v>
       </c>
       <c r="ACJ2" t="n">
-        <v>502134</v>
+        <v>750970</v>
       </c>
       <c r="ACK2" t="n">
-        <v>277727</v>
+        <v>1201871</v>
       </c>
       <c r="ACL2" t="n">
-        <v>712013</v>
+        <v>1091640</v>
       </c>
       <c r="ACM2" t="n">
-        <v>49585</v>
+        <v>130723</v>
       </c>
       <c r="ACN2" t="n">
-        <v>725191</v>
+        <v>235415</v>
       </c>
       <c r="ACO2" t="n">
-        <v>787678</v>
+        <v>139570</v>
       </c>
       <c r="ACP2" t="n">
-        <v>71321</v>
+        <v>135529</v>
       </c>
       <c r="ACQ2" t="n">
-        <v>709333</v>
+        <v>84378</v>
       </c>
       <c r="ACR2" t="n">
-        <v>159787</v>
+        <v>308102</v>
       </c>
       <c r="ACS2" t="n">
-        <v>798657</v>
+        <v>365330</v>
       </c>
       <c r="ACT2" t="n">
-        <v>285251</v>
+        <v>885494</v>
       </c>
       <c r="ACU2" t="n">
-        <v>1087445</v>
+        <v>843754</v>
       </c>
       <c r="ACV2" t="n">
-        <v>621342</v>
+        <v>1080529</v>
       </c>
       <c r="ACW2" t="n">
-        <v>217781</v>
+        <v>853347</v>
       </c>
       <c r="ACX2" t="n">
-        <v>1112482</v>
+        <v>56207</v>
       </c>
       <c r="ACY2" t="n">
-        <v>311746</v>
+        <v>683412</v>
       </c>
       <c r="ACZ2" t="n">
-        <v>146022</v>
+        <v>339753</v>
       </c>
       <c r="ADA2" t="n">
-        <v>907766</v>
+        <v>67527</v>
       </c>
       <c r="ADB2" t="n">
-        <v>1180165</v>
+        <v>183286</v>
       </c>
       <c r="ADC2" t="n">
-        <v>654744</v>
+        <v>40918</v>
       </c>
       <c r="ADD2" t="n">
-        <v>270236</v>
+        <v>1148448</v>
       </c>
       <c r="ADE2" t="n">
-        <v>986138</v>
+        <v>249652</v>
       </c>
       <c r="ADF2" t="n">
-        <v>1111349</v>
+        <v>613205</v>
       </c>
       <c r="ADG2" t="n">
-        <v>86997</v>
+        <v>474247</v>
       </c>
       <c r="ADH2" t="n">
-        <v>443116</v>
+        <v>24851</v>
       </c>
       <c r="ADI2" t="n">
-        <v>100921</v>
+        <v>69598</v>
       </c>
       <c r="ADJ2" t="n">
-        <v>94311</v>
+        <v>722561</v>
       </c>
       <c r="ADK2" t="n">
-        <v>671306</v>
+        <v>72392</v>
       </c>
       <c r="ADL2" t="n">
-        <v>1103808</v>
+        <v>113476</v>
       </c>
       <c r="ADM2" t="n">
-        <v>159607</v>
+        <v>360425</v>
       </c>
       <c r="ADN2" t="n">
-        <v>544051</v>
+        <v>154497</v>
       </c>
       <c r="ADO2" t="n">
-        <v>1078650</v>
+        <v>177578</v>
       </c>
       <c r="ADP2" t="n">
-        <v>366717</v>
+        <v>768202</v>
       </c>
       <c r="ADQ2" t="n">
-        <v>276383</v>
+        <v>1041767</v>
       </c>
       <c r="ADR2" t="n">
-        <v>802550</v>
+        <v>1029438</v>
       </c>
       <c r="ADS2" t="n">
-        <v>445066</v>
+        <v>576870</v>
       </c>
       <c r="ADT2" t="n">
-        <v>530753</v>
+        <v>346651</v>
       </c>
       <c r="ADU2" t="n">
-        <v>192264</v>
+        <v>1109336</v>
       </c>
       <c r="ADV2" t="n">
-        <v>860820</v>
+        <v>310904</v>
       </c>
       <c r="ADW2" t="n">
-        <v>468731</v>
+        <v>280878</v>
       </c>
       <c r="ADX2" t="n">
-        <v>1169600</v>
+        <v>496185</v>
       </c>
       <c r="ADY2" t="n">
-        <v>285649</v>
+        <v>830183</v>
       </c>
       <c r="ADZ2" t="n">
-        <v>370047</v>
+        <v>612710</v>
       </c>
       <c r="AEA2" t="n">
-        <v>601952</v>
+        <v>70651</v>
       </c>
       <c r="AEB2" t="n">
-        <v>735983</v>
+        <v>266595</v>
       </c>
       <c r="AEC2" t="n">
-        <v>574141</v>
+        <v>1023329</v>
       </c>
       <c r="AED2" t="n">
-        <v>885462</v>
+        <v>253428</v>
       </c>
       <c r="AEE2" t="n">
-        <v>471745</v>
+        <v>268656</v>
       </c>
       <c r="AEF2" t="n">
-        <v>838453</v>
+        <v>537293</v>
       </c>
       <c r="AEG2" t="n">
-        <v>865347</v>
+        <v>999114</v>
       </c>
       <c r="AEH2" t="n">
-        <v>432804</v>
+        <v>414183</v>
       </c>
       <c r="AEI2" t="n">
-        <v>667973</v>
+        <v>10785</v>
       </c>
       <c r="AEJ2" t="n">
-        <v>851743</v>
+        <v>274487</v>
       </c>
       <c r="AEK2" t="n">
-        <v>298224</v>
+        <v>205688</v>
       </c>
       <c r="AEL2" t="n">
-        <v>451584</v>
+        <v>746777</v>
       </c>
       <c r="AEM2" t="n">
-        <v>965338</v>
+        <v>201521</v>
       </c>
       <c r="AEN2" t="n">
-        <v>943404</v>
+        <v>1004176</v>
       </c>
       <c r="AEO2" t="n">
-        <v>1165821</v>
+        <v>702891</v>
       </c>
       <c r="AEP2" t="n">
-        <v>233587</v>
+        <v>913015</v>
       </c>
       <c r="AEQ2" t="n">
-        <v>105051</v>
+        <v>978659</v>
       </c>
       <c r="AER2" t="n">
-        <v>185665</v>
+        <v>1136806</v>
       </c>
       <c r="AES2" t="n">
-        <v>1044284</v>
+        <v>785519</v>
       </c>
       <c r="AET2" t="n">
-        <v>881251</v>
+        <v>238685</v>
       </c>
       <c r="AEU2" t="n">
-        <v>378603</v>
+        <v>98849</v>
       </c>
       <c r="AEV2" t="n">
-        <v>74854</v>
+        <v>432466</v>
       </c>
       <c r="AEW2" t="n">
-        <v>465766</v>
+        <v>1113974</v>
       </c>
       <c r="AEX2" t="n">
-        <v>644973</v>
+        <v>876179</v>
       </c>
       <c r="AEY2" t="n">
-        <v>972731</v>
+        <v>65904</v>
       </c>
       <c r="AEZ2" t="n">
-        <v>32386</v>
+        <v>220388</v>
       </c>
       <c r="AFA2" t="n">
-        <v>435729</v>
+        <v>119676</v>
       </c>
       <c r="AFB2" t="n">
-        <v>202905</v>
+        <v>952442</v>
       </c>
       <c r="AFC2" t="n">
-        <v>135039</v>
+        <v>685944</v>
       </c>
       <c r="AFD2" t="n">
-        <v>976484</v>
+        <v>153896</v>
       </c>
       <c r="AFE2" t="n">
-        <v>41318</v>
+        <v>951138</v>
       </c>
       <c r="AFF2" t="n">
-        <v>773595</v>
+        <v>1151215</v>
       </c>
       <c r="AFG2" t="n">
-        <v>52544</v>
+        <v>101230</v>
       </c>
       <c r="AFH2" t="n">
-        <v>1143682</v>
+        <v>637967</v>
       </c>
       <c r="AFI2" t="n">
-        <v>800413</v>
+        <v>254371</v>
       </c>
       <c r="AFJ2" t="n">
-        <v>573948</v>
+        <v>812329</v>
       </c>
       <c r="AFK2" t="n">
-        <v>132832</v>
+        <v>112372</v>
       </c>
       <c r="AFL2" t="n">
-        <v>448645</v>
+        <v>1194367</v>
       </c>
       <c r="AFM2" t="n">
-        <v>957123</v>
+        <v>870954</v>
       </c>
       <c r="AFN2" t="n">
-        <v>365241</v>
+        <v>747434</v>
       </c>
       <c r="AFO2" t="n">
-        <v>931079</v>
+        <v>984025</v>
       </c>
       <c r="AFP2" t="n">
-        <v>257664</v>
+        <v>1060180</v>
       </c>
       <c r="AFQ2" t="n">
-        <v>1139696</v>
+        <v>833354</v>
       </c>
       <c r="AFR2" t="n">
-        <v>815678</v>
+        <v>758446</v>
       </c>
       <c r="AFS2" t="n">
-        <v>1108716</v>
+        <v>163726</v>
       </c>
       <c r="AFT2" t="n">
-        <v>486222</v>
+        <v>382533</v>
       </c>
       <c r="AFU2" t="n">
-        <v>23685</v>
+        <v>490991</v>
       </c>
       <c r="AFV2" t="n">
-        <v>1105093</v>
+        <v>960385</v>
       </c>
       <c r="AFW2" t="n">
-        <v>890522</v>
+        <v>474144</v>
       </c>
       <c r="AFX2" t="n">
-        <v>413921</v>
+        <v>980846</v>
       </c>
       <c r="AFY2" t="n">
-        <v>686880</v>
+        <v>706458</v>
       </c>
       <c r="AFZ2" t="n">
-        <v>257472</v>
+        <v>846467</v>
       </c>
       <c r="AGA2" t="n">
-        <v>377037</v>
+        <v>126447</v>
       </c>
       <c r="AGB2" t="n">
-        <v>936856</v>
+        <v>394910</v>
       </c>
       <c r="AGC2" t="n">
-        <v>1158382</v>
+        <v>128763</v>
       </c>
       <c r="AGD2" t="n">
-        <v>988166</v>
+        <v>448525</v>
       </c>
       <c r="AGE2" t="n">
-        <v>28209</v>
+        <v>670684</v>
       </c>
       <c r="AGF2" t="n">
-        <v>1076489</v>
+        <v>826504</v>
       </c>
       <c r="AGG2" t="n">
-        <v>522788</v>
+        <v>1139971</v>
       </c>
       <c r="AGH2" t="n">
-        <v>244185</v>
+        <v>945559</v>
       </c>
       <c r="AGI2" t="n">
-        <v>443818</v>
+        <v>300211</v>
       </c>
       <c r="AGJ2" t="n">
-        <v>218117</v>
+        <v>433951</v>
       </c>
       <c r="AGK2" t="n">
-        <v>1199543</v>
+        <v>1211312</v>
       </c>
       <c r="AGL2" t="n">
-        <v>1023306</v>
+        <v>163625</v>
       </c>
       <c r="AGM2" t="n">
-        <v>876039</v>
+        <v>388604</v>
       </c>
       <c r="AGN2" t="n">
-        <v>1082813</v>
+        <v>938119</v>
       </c>
       <c r="AGO2" t="n">
-        <v>756400</v>
+        <v>879776</v>
       </c>
       <c r="AGP2" t="n">
-        <v>28149</v>
+        <v>542163</v>
       </c>
       <c r="AGQ2" t="n">
-        <v>816500</v>
+        <v>419574</v>
       </c>
       <c r="AGR2" t="n">
-        <v>603712</v>
+        <v>1062421</v>
       </c>
       <c r="AGS2" t="n">
-        <v>415050</v>
+        <v>189478</v>
       </c>
       <c r="AGT2" t="n">
-        <v>679861</v>
+        <v>98366</v>
       </c>
       <c r="AGU2" t="n">
-        <v>333025</v>
+        <v>442967</v>
       </c>
       <c r="AGV2" t="n">
-        <v>1115721</v>
+        <v>1220417</v>
       </c>
       <c r="AGW2" t="n">
-        <v>423614</v>
+        <v>1075655</v>
       </c>
       <c r="AGX2" t="n">
-        <v>1046318</v>
+        <v>579378</v>
       </c>
       <c r="AGY2" t="n">
-        <v>356243</v>
+        <v>792604</v>
       </c>
       <c r="AGZ2" t="n">
-        <v>573172</v>
+        <v>514232</v>
       </c>
       <c r="AHA2" t="n">
-        <v>478113</v>
+        <v>71080</v>
       </c>
       <c r="AHB2" t="n">
-        <v>183547</v>
+        <v>136483</v>
       </c>
       <c r="AHC2" t="n">
-        <v>109702</v>
+        <v>1098805</v>
       </c>
       <c r="AHD2" t="n">
-        <v>834762</v>
+        <v>248726</v>
       </c>
       <c r="AHE2" t="n">
-        <v>75940</v>
+        <v>328810</v>
       </c>
       <c r="AHF2" t="n">
-        <v>279363</v>
+        <v>1051328</v>
       </c>
       <c r="AHG2" t="n">
-        <v>482850</v>
+        <v>491812</v>
       </c>
       <c r="AHH2" t="n">
-        <v>72688</v>
+        <v>500966</v>
       </c>
       <c r="AHI2" t="n">
-        <v>455870</v>
+        <v>511791</v>
       </c>
       <c r="AHJ2" t="n">
-        <v>1035792</v>
+        <v>526975</v>
       </c>
       <c r="AHK2" t="n">
-        <v>1081068</v>
+        <v>623773</v>
       </c>
       <c r="AHL2" t="n">
-        <v>376086</v>
+        <v>77106</v>
       </c>
       <c r="AHM2" t="n">
-        <v>89731</v>
+        <v>1144055</v>
       </c>
       <c r="AHN2" t="n">
-        <v>935107</v>
+        <v>401356</v>
       </c>
       <c r="AHO2" t="n">
-        <v>1071157</v>
+        <v>199531</v>
       </c>
       <c r="AHP2" t="n">
-        <v>952753</v>
+        <v>682889</v>
       </c>
       <c r="AHQ2" t="n">
-        <v>886841</v>
+        <v>271929</v>
       </c>
       <c r="AHR2" t="n">
-        <v>164426</v>
+        <v>27517</v>
       </c>
       <c r="AHS2" t="n">
-        <v>409316</v>
+        <v>564821</v>
       </c>
       <c r="AHT2" t="n">
-        <v>790322</v>
+        <v>665796</v>
       </c>
       <c r="AHU2" t="n">
-        <v>194003</v>
+        <v>6327</v>
       </c>
       <c r="AHV2" t="n">
-        <v>389860</v>
+        <v>215570</v>
       </c>
       <c r="AHW2" t="n">
-        <v>453295</v>
+        <v>1045526</v>
       </c>
       <c r="AHX2" t="n">
-        <v>621106</v>
+        <v>2666</v>
       </c>
       <c r="AHY2" t="n">
-        <v>716768</v>
+        <v>335851</v>
       </c>
       <c r="AHZ2" t="n">
-        <v>93781</v>
+        <v>437883</v>
       </c>
       <c r="AIA2" t="n">
-        <v>462282</v>
+        <v>263152</v>
       </c>
       <c r="AIB2" t="n">
-        <v>1207928</v>
+        <v>279039</v>
       </c>
       <c r="AIC2" t="n">
-        <v>265947</v>
+        <v>737511</v>
       </c>
       <c r="AID2" t="n">
-        <v>379908</v>
+        <v>1184427</v>
       </c>
       <c r="AIE2" t="n">
-        <v>906891</v>
+        <v>475459</v>
       </c>
       <c r="AIF2" t="n">
-        <v>1204657</v>
+        <v>341941</v>
       </c>
       <c r="AIG2" t="n">
-        <v>725883</v>
+        <v>231006</v>
       </c>
       <c r="AIH2" t="n">
-        <v>697760</v>
+        <v>653833</v>
       </c>
       <c r="AII2" t="n">
-        <v>1133665</v>
+        <v>567947</v>
       </c>
       <c r="AIJ2" t="n">
-        <v>60635</v>
+        <v>1057566</v>
       </c>
       <c r="AIK2" t="n">
-        <v>515857</v>
+        <v>305449</v>
       </c>
       <c r="AIL2" t="n">
-        <v>1053159</v>
+        <v>277463</v>
       </c>
       <c r="AIM2" t="n">
-        <v>774864</v>
+        <v>898268</v>
       </c>
       <c r="AIN2" t="n">
-        <v>607096</v>
+        <v>762620</v>
       </c>
       <c r="AIO2" t="n">
-        <v>668700</v>
+        <v>713909</v>
       </c>
       <c r="AIP2" t="n">
-        <v>309990</v>
+        <v>704260</v>
       </c>
       <c r="AIQ2" t="n">
-        <v>1141300</v>
+        <v>667319</v>
       </c>
       <c r="AIR2" t="n">
-        <v>380128</v>
+        <v>1185330</v>
       </c>
       <c r="AIS2" t="n">
-        <v>860628</v>
+        <v>629888</v>
       </c>
       <c r="AIT2" t="n">
-        <v>761405</v>
+        <v>186963</v>
       </c>
       <c r="AIU2" t="n">
-        <v>762401</v>
+        <v>1120485</v>
       </c>
       <c r="AIV2" t="n">
-        <v>991326</v>
+        <v>804970</v>
       </c>
       <c r="AIW2" t="n">
-        <v>247572</v>
+        <v>88209</v>
       </c>
       <c r="AIX2" t="n">
-        <v>889580</v>
+        <v>1102366</v>
       </c>
       <c r="AIY2" t="n">
-        <v>1062426</v>
+        <v>1054594</v>
       </c>
       <c r="AIZ2" t="n">
-        <v>1082574</v>
+        <v>1127034</v>
       </c>
       <c r="AJA2" t="n">
-        <v>359193</v>
+        <v>347749</v>
       </c>
       <c r="AJB2" t="n">
-        <v>918668</v>
+        <v>64083</v>
       </c>
       <c r="AJC2" t="n">
-        <v>547171</v>
+        <v>52259</v>
       </c>
       <c r="AJD2" t="n">
-        <v>1178265</v>
+        <v>415708</v>
       </c>
       <c r="AJE2" t="n">
-        <v>325480</v>
+        <v>146570</v>
       </c>
       <c r="AJF2" t="n">
-        <v>747315</v>
+        <v>1096962</v>
       </c>
       <c r="AJG2" t="n">
-        <v>1016500</v>
+        <v>727485</v>
       </c>
       <c r="AJH2" t="n">
-        <v>57802</v>
+        <v>121730</v>
       </c>
       <c r="AJI2" t="n">
-        <v>1107826</v>
+        <v>775461</v>
       </c>
       <c r="AJJ2" t="n">
-        <v>1097284</v>
+        <v>192388</v>
       </c>
       <c r="AJK2" t="n">
-        <v>614249</v>
+        <v>142554</v>
       </c>
       <c r="AJL2" t="n">
-        <v>267840</v>
+        <v>3445</v>
       </c>
       <c r="AJM2" t="n">
-        <v>197731</v>
+        <v>397131</v>
       </c>
       <c r="AJN2" t="n">
-        <v>7849</v>
+        <v>210083</v>
       </c>
       <c r="AJO2" t="n">
-        <v>1196639</v>
+        <v>1020015</v>
       </c>
       <c r="AJP2" t="n">
-        <v>48604</v>
+        <v>923478</v>
       </c>
       <c r="AJQ2" t="n">
-        <v>119776</v>
+        <v>672017</v>
       </c>
       <c r="AJR2" t="n">
-        <v>349741</v>
+        <v>247786</v>
       </c>
       <c r="AJS2" t="n">
-        <v>65367</v>
+        <v>568538</v>
       </c>
       <c r="AJT2" t="n">
-        <v>659099</v>
+        <v>35698</v>
       </c>
       <c r="AJU2" t="n">
-        <v>166665</v>
+        <v>762588</v>
       </c>
       <c r="AJV2" t="n">
-        <v>1161326</v>
+        <v>1201284</v>
       </c>
       <c r="AJW2" t="n">
-        <v>593055</v>
+        <v>674994</v>
       </c>
       <c r="AJX2" t="n">
-        <v>1039018</v>
+        <v>1047178</v>
       </c>
       <c r="AJY2" t="n">
-        <v>804803</v>
+        <v>1110142</v>
       </c>
       <c r="AJZ2" t="n">
-        <v>714871</v>
+        <v>197101</v>
       </c>
       <c r="AKA2" t="n">
-        <v>983763</v>
+        <v>503708</v>
       </c>
       <c r="AKB2" t="n">
-        <v>447501</v>
+        <v>1155048</v>
       </c>
       <c r="AKC2" t="n">
-        <v>102678</v>
+        <v>715942</v>
       </c>
       <c r="AKD2" t="n">
-        <v>1092962</v>
+        <v>124582</v>
       </c>
       <c r="AKE2" t="n">
-        <v>952912</v>
+        <v>84871</v>
       </c>
       <c r="AKF2" t="n">
-        <v>1095332</v>
+        <v>799343</v>
       </c>
       <c r="AKG2" t="n">
-        <v>636113</v>
+        <v>1152698</v>
       </c>
       <c r="AKH2" t="n">
-        <v>208221</v>
+        <v>318298</v>
       </c>
       <c r="AKI2" t="n">
-        <v>633350</v>
+        <v>850383</v>
       </c>
       <c r="AKJ2" t="n">
-        <v>795173</v>
+        <v>601622</v>
       </c>
       <c r="AKK2" t="n">
-        <v>495341</v>
+        <v>688650</v>
       </c>
       <c r="AKL2" t="n">
-        <v>894955</v>
+        <v>1042579</v>
       </c>
       <c r="AKM2" t="n">
-        <v>714977</v>
+        <v>915088</v>
       </c>
       <c r="AKN2" t="n">
-        <v>578525</v>
+        <v>817343</v>
       </c>
       <c r="AKO2" t="n">
-        <v>558841</v>
+        <v>294530</v>
       </c>
       <c r="AKP2" t="n">
-        <v>333989</v>
+        <v>1012207</v>
       </c>
       <c r="AKQ2" t="n">
-        <v>499370</v>
+        <v>471474</v>
       </c>
       <c r="AKR2" t="n">
-        <v>1067966</v>
+        <v>425323</v>
       </c>
       <c r="AKS2" t="n">
-        <v>163394</v>
+        <v>1090194</v>
       </c>
       <c r="AKT2" t="n">
-        <v>1210142</v>
+        <v>691025</v>
       </c>
       <c r="AKU2" t="n">
-        <v>246</v>
+        <v>27038</v>
       </c>
       <c r="AKV2" t="n">
-        <v>709410</v>
+        <v>1138202</v>
       </c>
       <c r="AKW2" t="n">
-        <v>5507</v>
+        <v>132397</v>
       </c>
       <c r="AKX2" t="n">
-        <v>1004105</v>
+        <v>721713</v>
       </c>
       <c r="AKY2" t="n">
-        <v>513980</v>
+        <v>985659</v>
       </c>
       <c r="AKZ2" t="n">
-        <v>638556</v>
+        <v>689718</v>
       </c>
       <c r="ALA2" t="n">
-        <v>209952</v>
+        <v>856842</v>
       </c>
       <c r="ALB2" t="n">
-        <v>773641</v>
+        <v>287113</v>
       </c>
       <c r="ALC2" t="n">
-        <v>123399</v>
+        <v>1097200</v>
       </c>
       <c r="ALD2" t="n">
-        <v>55521</v>
+        <v>109591</v>
       </c>
       <c r="ALE2" t="n">
-        <v>479335</v>
+        <v>899500</v>
       </c>
       <c r="ALF2" t="n">
-        <v>642496</v>
+        <v>123084</v>
       </c>
       <c r="ALG2" t="n">
-        <v>450576</v>
+        <v>630862</v>
       </c>
       <c r="ALH2" t="n">
-        <v>408085</v>
+        <v>986538</v>
       </c>
       <c r="ALI2" t="n">
-        <v>916160</v>
+        <v>227173</v>
       </c>
       <c r="ALJ2" t="n">
-        <v>900960</v>
+        <v>315204</v>
       </c>
       <c r="ALK2" t="n">
-        <v>569947</v>
+        <v>807914</v>
       </c>
       <c r="ALL2" t="n">
-        <v>914420</v>
+        <v>1043938</v>
       </c>
     </row>
   </sheetData>
